--- a/config/Excel/String.xlsx
+++ b/config/Excel/String.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB99E11-614E-4655-8A96-7ED7669CA346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE18A472-790D-47D1-B2EF-8D08A2E6562E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9991" uniqueCount="6651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9996" uniqueCount="6655">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -26241,6 +26241,18 @@
   <si>
     <t>推進關卡　{0} / {1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2130</t>
+  </si>
+  <si>
+    <t>世界地圖名稱下方目前關卡／場景上限</t>
+  </si>
+  <si>
+    <t>{0}=目前停留關卡；{1}=場景最大關卡</t>
+  </si>
+  <si>
+    <t>({0}/{1})</t>
   </si>
 </sst>
 </file>
@@ -26566,7 +26578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2117"/>
+  <dimension ref="A1:G2118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -60792,6 +60804,23 @@
         <v>6649</v>
       </c>
     </row>
+    <row r="2118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2118" s="1" t="s">
+        <v>6651</v>
+      </c>
+      <c r="B2118" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2118" s="1" t="s">
+        <v>6652</v>
+      </c>
+      <c r="D2118" s="1" t="s">
+        <v>6653</v>
+      </c>
+      <c r="E2118" s="1" t="s">
+        <v>6654</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/Excel/String.xlsx
+++ b/config/Excel/String.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB99E11-614E-4655-8A96-7ED7669CA346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A794E9D-0FE0-4E81-AB4A-48584C224090}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9991" uniqueCount="6651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10000" uniqueCount="6658">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -26241,6 +26241,27 @@
   <si>
     <t>推進關卡　{0} / {1}</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2130</t>
+  </si>
+  <si>
+    <t>提示｜ui.js setGemTool／renderGems 寶石共鳴頁籤（未解鎖）</t>
+  </si>
+  <si>
+    <t>寶石共鳴尚未解鎖</t>
+  </si>
+  <si>
+    <t>2131</t>
+  </si>
+  <si>
+    <t>提示／文字｜ui.js renderGems 寶石共鳴頁籤、gem_resonance.js 共鳴指令</t>
+  </si>
+  <si>
+    <t>{0}=解鎖等級（GEM_RESONANCE_UNLOCK_LEVEL）；{1}=解鎖轉生次數（GEM_RESONANCE_UNLOCK_REINCARNATION）</t>
+  </si>
+  <si>
+    <t>寶石共鳴需達到 {1} 轉且角色 Lv.{0} 才開放</t>
   </si>
 </sst>
 </file>
@@ -26566,7 +26587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2117"/>
+  <dimension ref="A1:G2119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -60792,6 +60813,37 @@
         <v>6649</v>
       </c>
     </row>
+    <row r="2118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2118" s="1" t="s">
+        <v>6651</v>
+      </c>
+      <c r="B2118" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2118" s="1" t="s">
+        <v>6652</v>
+      </c>
+      <c r="E2118" s="1" t="s">
+        <v>6653</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2119" s="1" t="s">
+        <v>6654</v>
+      </c>
+      <c r="B2119" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2119" s="1" t="s">
+        <v>6655</v>
+      </c>
+      <c r="D2119" s="1" t="s">
+        <v>6656</v>
+      </c>
+      <c r="E2119" s="1" t="s">
+        <v>6657</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/Excel/String.xlsx
+++ b/config/Excel/String.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F801EFB-FD7A-4190-9A5C-14467758FAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E3CEB6-B01D-431F-840F-01023FB3B785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="String" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10329" uniqueCount="6834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10333" uniqueCount="6837">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -26798,6 +26798,15 @@
   </si>
   <si>
     <t>神聖詞條 {0}倍；神聖鑲孔 {1}倍。</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>界面文字｜世界地圖神界傳送門</t>
+  </si>
+  <si>
+    <t>神界傳送門</t>
   </si>
 </sst>
 </file>
@@ -27123,7 +27132,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2193"/>
+  <dimension ref="A1:G2194"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
@@ -62555,6 +62564,20 @@
         <v>6699</v>
       </c>
     </row>
+    <row r="2194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2194" s="1" t="s">
+        <v>6834</v>
+      </c>
+      <c r="B2194" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2194" s="1" t="s">
+        <v>6835</v>
+      </c>
+      <c r="E2194" s="1" t="s">
+        <v>6836</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/Excel/String.xlsx
+++ b/config/Excel/String.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ED2390-2DF1-4E3A-8409-BDB5E0C8D611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E80208D-6FE0-4CD3-991A-6737F45DCF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10417" uniqueCount="6899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10417" uniqueCount="6904">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -26465,15 +26465,9 @@
     <t>2173</t>
   </si>
   <si>
-    <t>成功率 {0}%（基礎 {1}%＋神性之石 {2}%）</t>
-  </si>
-  <si>
     <t>2174</t>
   </si>
   <si>
-    <t>神性之石：持有 {0}，本次使用 {1}／最多 {2}</t>
-  </si>
-  <si>
     <t>2175</t>
   </si>
   <si>
@@ -26483,9 +26477,6 @@
     <t>2176</t>
   </si>
   <si>
-    <t>放入素材後顯示成功率與金幣費用。</t>
-  </si>
-  <si>
     <t>2177</t>
   </si>
   <si>
@@ -26992,6 +26983,38 @@
   </si>
   <si>
     <t>把寶石鑲入共鳴鑲孔中以獲取寶石能力。&lt;br&gt;升級鑲孔可獲得相鄰寶石效果的額外加成，僅限不同類型寶石，同類型無法獲得。&lt;br&gt;同孔有多顆寶石時，只要其中一顆與相鄰寶石類型不同，即可獲得該相鄰寶石的加成，每顆相鄰寶石只計算一次。&lt;br&gt;中央區將在周圍六大區鑲孔都升至10級時解鎖。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神鑄神性之石提示總成功率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}=總成功率百分比（數字）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成功率 {0}%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神鑄神性之石提示持有量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}=持有神性之石（數字縮寫）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神性之石：持有 {0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>神鑄未放素材時的成功率提示</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>放入素材後顯示成功率。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -28820,7 +28843,7 @@
         <v>451</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>6790</v>
+        <v>6787</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -34391,13 +34414,13 @@
         <v>186</v>
       </c>
       <c r="C450" s="1" t="s">
-        <v>6880</v>
+        <v>6877</v>
       </c>
       <c r="D450" s="1" t="s">
         <v>4230</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>6881</v>
+        <v>6878</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
@@ -34408,13 +34431,13 @@
         <v>186</v>
       </c>
       <c r="C451" s="1" t="s">
-        <v>6882</v>
+        <v>6879</v>
       </c>
       <c r="D451" s="1" t="s">
         <v>4231</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>6883</v>
+        <v>6880</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
@@ -35628,7 +35651,7 @@
         <v>453</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>6791</v>
+        <v>6788</v>
       </c>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
@@ -35645,7 +35668,7 @@
         <v>4247</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>6792</v>
+        <v>6789</v>
       </c>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
@@ -37767,7 +37790,7 @@
         <v>1484</v>
       </c>
       <c r="E656" s="1" t="s">
-        <v>6793</v>
+        <v>6790</v>
       </c>
     </row>
     <row r="657" spans="1:5" x14ac:dyDescent="0.25">
@@ -37835,7 +37858,7 @@
         <v>1493</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>6794</v>
+        <v>6791</v>
       </c>
     </row>
     <row r="661" spans="1:5" x14ac:dyDescent="0.25">
@@ -47161,7 +47184,7 @@
         <v>2556</v>
       </c>
       <c r="E1247" s="1" t="s">
-        <v>6795</v>
+        <v>6792</v>
       </c>
     </row>
     <row r="1248" spans="1:5" x14ac:dyDescent="0.25">
@@ -47175,7 +47198,7 @@
         <v>2557</v>
       </c>
       <c r="E1248" s="1" t="s">
-        <v>6796</v>
+        <v>6793</v>
       </c>
     </row>
     <row r="1249" spans="1:5" x14ac:dyDescent="0.25">
@@ -47493,7 +47516,7 @@
         <v>5560</v>
       </c>
       <c r="E1269" s="1" t="s">
-        <v>6797</v>
+        <v>6794</v>
       </c>
     </row>
     <row r="1270" spans="1:5" x14ac:dyDescent="0.25">
@@ -47765,7 +47788,7 @@
         <v>5578</v>
       </c>
       <c r="E1285" s="1" t="s">
-        <v>6798</v>
+        <v>6795</v>
       </c>
     </row>
     <row r="1286" spans="1:5" x14ac:dyDescent="0.25">
@@ -47850,7 +47873,7 @@
         <v>453</v>
       </c>
       <c r="E1290" s="1" t="s">
-        <v>6799</v>
+        <v>6796</v>
       </c>
     </row>
     <row r="1291" spans="1:5" x14ac:dyDescent="0.25">
@@ -47867,7 +47890,7 @@
         <v>4313</v>
       </c>
       <c r="E1291" s="1" t="s">
-        <v>6800</v>
+        <v>6797</v>
       </c>
     </row>
     <row r="1292" spans="1:5" x14ac:dyDescent="0.25">
@@ -47918,7 +47941,7 @@
         <v>4315</v>
       </c>
       <c r="E1294" s="1" t="s">
-        <v>6801</v>
+        <v>6798</v>
       </c>
     </row>
     <row r="1295" spans="1:5" x14ac:dyDescent="0.25">
@@ -48105,7 +48128,7 @@
         <v>453</v>
       </c>
       <c r="E1305" s="1" t="s">
-        <v>6802</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="1306" spans="1:5" x14ac:dyDescent="0.25">
@@ -48170,7 +48193,7 @@
         <v>5605</v>
       </c>
       <c r="E1309" s="1" t="s">
-        <v>6803</v>
+        <v>6800</v>
       </c>
     </row>
     <row r="1310" spans="1:5" x14ac:dyDescent="0.25">
@@ -48215,7 +48238,7 @@
         <v>2676</v>
       </c>
       <c r="E1312" s="1" t="s">
-        <v>6804</v>
+        <v>6801</v>
       </c>
     </row>
     <row r="1313" spans="1:5" x14ac:dyDescent="0.25">
@@ -48543,7 +48566,7 @@
         <v>2745</v>
       </c>
       <c r="E1332" s="1" t="s">
-        <v>6805</v>
+        <v>6802</v>
       </c>
     </row>
     <row r="1333" spans="1:5" x14ac:dyDescent="0.25">
@@ -48560,7 +48583,7 @@
         <v>6481</v>
       </c>
       <c r="E1333" s="1" t="s">
-        <v>6806</v>
+        <v>6803</v>
       </c>
     </row>
     <row r="1334" spans="1:5" x14ac:dyDescent="0.25">
@@ -48679,7 +48702,7 @@
         <v>6483</v>
       </c>
       <c r="E1340" s="1" t="s">
-        <v>6807</v>
+        <v>6804</v>
       </c>
     </row>
     <row r="1341" spans="1:5" x14ac:dyDescent="0.25">
@@ -48713,7 +48736,7 @@
         <v>5644</v>
       </c>
       <c r="E1342" s="1" t="s">
-        <v>6808</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="1343" spans="1:5" x14ac:dyDescent="0.25">
@@ -48925,7 +48948,7 @@
         <v>2779</v>
       </c>
       <c r="E1355" s="1" t="s">
-        <v>6809</v>
+        <v>6806</v>
       </c>
     </row>
     <row r="1356" spans="1:5" x14ac:dyDescent="0.25">
@@ -48942,7 +48965,7 @@
         <v>453</v>
       </c>
       <c r="E1356" s="1" t="s">
-        <v>6810</v>
+        <v>6807</v>
       </c>
     </row>
     <row r="1357" spans="1:5" x14ac:dyDescent="0.25">
@@ -49219,10 +49242,10 @@
         <v>6696</v>
       </c>
       <c r="D1374" s="1" t="s">
-        <v>6814</v>
+        <v>6811</v>
       </c>
       <c r="E1374" s="1" t="s">
-        <v>6815</v>
+        <v>6812</v>
       </c>
     </row>
     <row r="1375" spans="1:5" x14ac:dyDescent="0.25">
@@ -49236,10 +49259,10 @@
         <v>6696</v>
       </c>
       <c r="D1375" s="1" t="s">
-        <v>6814</v>
+        <v>6811</v>
       </c>
       <c r="E1375" s="1" t="s">
-        <v>6816</v>
+        <v>6813</v>
       </c>
     </row>
     <row r="1376" spans="1:5" x14ac:dyDescent="0.25">
@@ -49346,35 +49369,35 @@
         <v>25</v>
       </c>
       <c r="C1382" s="1" t="s">
-        <v>6696</v>
+        <v>6896</v>
       </c>
       <c r="D1382" s="1" t="s">
-        <v>6709</v>
+        <v>6897</v>
       </c>
       <c r="E1382" s="1" t="s">
-        <v>6734</v>
+        <v>6898</v>
       </c>
     </row>
     <row r="1383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1383" s="1" t="s">
-        <v>6735</v>
+        <v>6734</v>
       </c>
       <c r="B1383" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1383" s="1" t="s">
-        <v>6696</v>
+        <v>6899</v>
       </c>
       <c r="D1383" s="1" t="s">
-        <v>6709</v>
+        <v>6900</v>
       </c>
       <c r="E1383" s="1" t="s">
-        <v>6736</v>
+        <v>6901</v>
       </c>
     </row>
     <row r="1384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1384" s="1" t="s">
-        <v>6737</v>
+        <v>6735</v>
       </c>
       <c r="B1384" s="1" t="s">
         <v>25</v>
@@ -49386,27 +49409,27 @@
         <v>6709</v>
       </c>
       <c r="E1384" s="1" t="s">
-        <v>6738</v>
+        <v>6736</v>
       </c>
     </row>
     <row r="1385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1385" s="1" t="s">
-        <v>6739</v>
+        <v>6737</v>
       </c>
       <c r="B1385" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1385" s="1" t="s">
-        <v>6696</v>
+        <v>6902</v>
       </c>
       <c r="D1385" s="1"/>
       <c r="E1385" s="1" t="s">
-        <v>6740</v>
+        <v>6903</v>
       </c>
     </row>
     <row r="1386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1386" s="1" t="s">
-        <v>6741</v>
+        <v>6738</v>
       </c>
       <c r="B1386" s="1" t="s">
         <v>25</v>
@@ -49418,12 +49441,12 @@
         <v>6709</v>
       </c>
       <c r="E1386" s="1" t="s">
-        <v>6742</v>
+        <v>6739</v>
       </c>
     </row>
     <row r="1387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1387" s="1" t="s">
-        <v>6743</v>
+        <v>6740</v>
       </c>
       <c r="B1387" s="1" t="s">
         <v>25</v>
@@ -49433,12 +49456,12 @@
       </c>
       <c r="D1387" s="1"/>
       <c r="E1387" s="1" t="s">
-        <v>6744</v>
+        <v>6741</v>
       </c>
     </row>
     <row r="1388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1388" s="1" t="s">
-        <v>6745</v>
+        <v>6742</v>
       </c>
       <c r="B1388" s="1" t="s">
         <v>25</v>
@@ -49448,12 +49471,12 @@
       </c>
       <c r="D1388" s="1"/>
       <c r="E1388" s="1" t="s">
-        <v>6746</v>
+        <v>6743</v>
       </c>
     </row>
     <row r="1389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1389" s="1" t="s">
-        <v>6747</v>
+        <v>6744</v>
       </c>
       <c r="B1389" s="1" t="s">
         <v>25</v>
@@ -49463,12 +49486,12 @@
       </c>
       <c r="D1389" s="1"/>
       <c r="E1389" s="1" t="s">
-        <v>6748</v>
+        <v>6745</v>
       </c>
     </row>
     <row r="1390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1390" s="1" t="s">
-        <v>6749</v>
+        <v>6746</v>
       </c>
       <c r="B1390" s="1" t="s">
         <v>25</v>
@@ -49478,12 +49501,12 @@
       </c>
       <c r="D1390" s="1"/>
       <c r="E1390" s="1" t="s">
-        <v>6750</v>
+        <v>6747</v>
       </c>
     </row>
     <row r="1391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1391" s="1" t="s">
-        <v>6751</v>
+        <v>6748</v>
       </c>
       <c r="B1391" s="1" t="s">
         <v>25</v>
@@ -49493,12 +49516,12 @@
       </c>
       <c r="D1391" s="1"/>
       <c r="E1391" s="1" t="s">
-        <v>6752</v>
+        <v>6749</v>
       </c>
     </row>
     <row r="1392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1392" s="1" t="s">
-        <v>6753</v>
+        <v>6750</v>
       </c>
       <c r="B1392" s="1" t="s">
         <v>25</v>
@@ -49508,12 +49531,12 @@
       </c>
       <c r="D1392" s="1"/>
       <c r="E1392" s="1" t="s">
-        <v>6754</v>
+        <v>6751</v>
       </c>
     </row>
     <row r="1393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1393" s="1" t="s">
-        <v>6755</v>
+        <v>6752</v>
       </c>
       <c r="B1393" s="1" t="s">
         <v>25</v>
@@ -49522,15 +49545,15 @@
         <v>6696</v>
       </c>
       <c r="D1393" s="1" t="s">
+        <v>6811</v>
+      </c>
+      <c r="E1393" s="1" t="s">
         <v>6814</v>
-      </c>
-      <c r="E1393" s="1" t="s">
-        <v>6817</v>
       </c>
     </row>
     <row r="1394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1394" s="1" t="s">
-        <v>6756</v>
+        <v>6753</v>
       </c>
       <c r="B1394" s="1" t="s">
         <v>25</v>
@@ -49540,12 +49563,12 @@
       </c>
       <c r="D1394" s="1"/>
       <c r="E1394" s="1" t="s">
-        <v>6757</v>
+        <v>6754</v>
       </c>
     </row>
     <row r="1395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1395" s="1" t="s">
-        <v>6758</v>
+        <v>6755</v>
       </c>
       <c r="B1395" s="1" t="s">
         <v>25</v>
@@ -49555,12 +49578,12 @@
       </c>
       <c r="D1395" s="1"/>
       <c r="E1395" s="1" t="s">
-        <v>6759</v>
+        <v>6756</v>
       </c>
     </row>
     <row r="1396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1396" s="1" t="s">
-        <v>6760</v>
+        <v>6757</v>
       </c>
       <c r="B1396" s="1" t="s">
         <v>25</v>
@@ -49570,12 +49593,12 @@
       </c>
       <c r="D1396" s="1"/>
       <c r="E1396" s="1" t="s">
-        <v>6761</v>
+        <v>6758</v>
       </c>
     </row>
     <row r="1397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1397" s="1" t="s">
-        <v>6762</v>
+        <v>6759</v>
       </c>
       <c r="B1397" s="1" t="s">
         <v>25</v>
@@ -49585,12 +49608,12 @@
       </c>
       <c r="D1397" s="1"/>
       <c r="E1397" s="1" t="s">
-        <v>6763</v>
+        <v>6760</v>
       </c>
     </row>
     <row r="1398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1398" s="1" t="s">
-        <v>6764</v>
+        <v>6761</v>
       </c>
       <c r="B1398" s="1" t="s">
         <v>25</v>
@@ -49600,12 +49623,12 @@
       </c>
       <c r="D1398" s="1"/>
       <c r="E1398" s="1" t="s">
-        <v>6765</v>
+        <v>6762</v>
       </c>
     </row>
     <row r="1399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1399" s="1" t="s">
-        <v>6766</v>
+        <v>6763</v>
       </c>
       <c r="B1399" s="1" t="s">
         <v>25</v>
@@ -49615,12 +49638,12 @@
       </c>
       <c r="D1399" s="1"/>
       <c r="E1399" s="1" t="s">
-        <v>6767</v>
+        <v>6764</v>
       </c>
     </row>
     <row r="1400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1400" s="1" t="s">
-        <v>6768</v>
+        <v>6765</v>
       </c>
       <c r="B1400" s="1" t="s">
         <v>25</v>
@@ -49632,12 +49655,12 @@
         <v>6709</v>
       </c>
       <c r="E1400" s="1" t="s">
-        <v>6769</v>
+        <v>6766</v>
       </c>
     </row>
     <row r="1401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1401" s="1" t="s">
-        <v>6770</v>
+        <v>6767</v>
       </c>
       <c r="B1401" s="1" t="s">
         <v>25</v>
@@ -49652,7 +49675,7 @@
     </row>
     <row r="1402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1402" s="1" t="s">
-        <v>6771</v>
+        <v>6768</v>
       </c>
       <c r="B1402" s="1" t="s">
         <v>25</v>
@@ -49661,15 +49684,15 @@
         <v>6696</v>
       </c>
       <c r="D1402" s="1" t="s">
-        <v>6814</v>
+        <v>6811</v>
       </c>
       <c r="E1402" s="1" t="s">
-        <v>6818</v>
+        <v>6815</v>
       </c>
     </row>
     <row r="1403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1403" s="1" t="s">
-        <v>6772</v>
+        <v>6769</v>
       </c>
       <c r="B1403" s="1" t="s">
         <v>25</v>
@@ -49679,12 +49702,12 @@
       </c>
       <c r="D1403" s="1"/>
       <c r="E1403" s="1" t="s">
-        <v>6773</v>
+        <v>6770</v>
       </c>
     </row>
     <row r="1404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1404" s="1" t="s">
-        <v>6774</v>
+        <v>6771</v>
       </c>
       <c r="B1404" s="1" t="s">
         <v>25</v>
@@ -49693,15 +49716,15 @@
         <v>6696</v>
       </c>
       <c r="D1404" s="1" t="s">
-        <v>6814</v>
+        <v>6811</v>
       </c>
       <c r="E1404" s="1" t="s">
-        <v>6819</v>
+        <v>6816</v>
       </c>
     </row>
     <row r="1405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1405" s="1" t="s">
-        <v>6775</v>
+        <v>6772</v>
       </c>
       <c r="B1405" s="1" t="s">
         <v>25</v>
@@ -49710,15 +49733,15 @@
         <v>6696</v>
       </c>
       <c r="D1405" s="1" t="s">
-        <v>6814</v>
+        <v>6811</v>
       </c>
       <c r="E1405" s="1" t="s">
-        <v>6820</v>
+        <v>6817</v>
       </c>
     </row>
     <row r="1406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1406" s="1" t="s">
-        <v>6776</v>
+        <v>6773</v>
       </c>
       <c r="B1406" s="1" t="s">
         <v>25</v>
@@ -49728,12 +49751,12 @@
       </c>
       <c r="D1406" s="1"/>
       <c r="E1406" s="1" t="s">
-        <v>6777</v>
+        <v>6774</v>
       </c>
     </row>
     <row r="1407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1407" s="1" t="s">
-        <v>6778</v>
+        <v>6775</v>
       </c>
       <c r="B1407" s="1" t="s">
         <v>25</v>
@@ -49745,12 +49768,12 @@
         <v>6709</v>
       </c>
       <c r="E1407" s="1" t="s">
-        <v>6779</v>
+        <v>6776</v>
       </c>
     </row>
     <row r="1408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1408" s="1" t="s">
-        <v>6780</v>
+        <v>6777</v>
       </c>
       <c r="B1408" s="1" t="s">
         <v>25</v>
@@ -49760,12 +49783,12 @@
       </c>
       <c r="D1408" s="1"/>
       <c r="E1408" s="1" t="s">
-        <v>6781</v>
+        <v>6778</v>
       </c>
     </row>
     <row r="1409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1409" s="1" t="s">
-        <v>6782</v>
+        <v>6779</v>
       </c>
       <c r="B1409" s="1" t="s">
         <v>25</v>
@@ -49777,12 +49800,12 @@
         <v>6709</v>
       </c>
       <c r="E1409" s="1" t="s">
-        <v>6783</v>
+        <v>6780</v>
       </c>
     </row>
     <row r="1410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1410" s="1" t="s">
-        <v>6784</v>
+        <v>6781</v>
       </c>
       <c r="B1410" s="1" t="s">
         <v>25</v>
@@ -49794,12 +49817,12 @@
         <v>6709</v>
       </c>
       <c r="E1410" s="1" t="s">
-        <v>6785</v>
+        <v>6782</v>
       </c>
     </row>
     <row r="1411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1411" s="1" t="s">
-        <v>6786</v>
+        <v>6783</v>
       </c>
       <c r="B1411" s="1" t="s">
         <v>25</v>
@@ -49809,12 +49832,12 @@
       </c>
       <c r="D1411" s="1"/>
       <c r="E1411" s="1" t="s">
-        <v>6787</v>
+        <v>6784</v>
       </c>
     </row>
     <row r="1412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1412" s="1" t="s">
-        <v>6788</v>
+        <v>6785</v>
       </c>
       <c r="B1412" s="1" t="s">
         <v>25</v>
@@ -49826,163 +49849,163 @@
         <v>6709</v>
       </c>
       <c r="E1412" s="1" t="s">
-        <v>6789</v>
+        <v>6786</v>
       </c>
     </row>
     <row r="1413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1413" s="1" t="s">
-        <v>6821</v>
+        <v>6818</v>
       </c>
       <c r="B1413" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1413" s="1" t="s">
-        <v>6822</v>
+        <v>6819</v>
       </c>
       <c r="D1413" s="1" t="s">
-        <v>6823</v>
+        <v>6820</v>
       </c>
       <c r="E1413" s="1" t="s">
-        <v>6824</v>
+        <v>6821</v>
       </c>
     </row>
     <row r="1414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1414" s="1" t="s">
-        <v>6825</v>
+        <v>6822</v>
       </c>
       <c r="B1414" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1414" s="1" t="s">
-        <v>6826</v>
+        <v>6823</v>
       </c>
       <c r="D1414" s="1" t="s">
-        <v>6827</v>
+        <v>6824</v>
       </c>
       <c r="E1414" s="1" t="s">
-        <v>6828</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="1415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1415" s="1" t="s">
-        <v>6832</v>
+        <v>6829</v>
       </c>
       <c r="B1415" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1415" s="1" t="s">
-        <v>6833</v>
+        <v>6830</v>
       </c>
       <c r="D1415" s="1"/>
       <c r="E1415" s="1" t="s">
-        <v>6834</v>
+        <v>6831</v>
       </c>
     </row>
     <row r="1416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1416" s="1" t="s">
-        <v>6835</v>
+        <v>6832</v>
       </c>
       <c r="B1416" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1416" s="1" t="s">
-        <v>6836</v>
+        <v>6833</v>
       </c>
       <c r="D1416" s="1"/>
       <c r="E1416" s="1" t="s">
-        <v>6837</v>
+        <v>6834</v>
       </c>
     </row>
     <row r="1417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1417" s="1" t="s">
-        <v>6838</v>
+        <v>6835</v>
       </c>
       <c r="B1417" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1417" s="1" t="s">
-        <v>6839</v>
+        <v>6836</v>
       </c>
       <c r="D1417" s="1"/>
       <c r="E1417" s="1" t="s">
-        <v>6840</v>
+        <v>6837</v>
       </c>
     </row>
     <row r="1418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1418" s="1" t="s">
-        <v>6841</v>
+        <v>6838</v>
       </c>
       <c r="B1418" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1418" s="1" t="s">
-        <v>6842</v>
+        <v>6839</v>
       </c>
       <c r="D1418" s="1"/>
       <c r="E1418" s="1" t="s">
-        <v>6843</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="1419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1419" s="1" t="s">
-        <v>6844</v>
+        <v>6841</v>
       </c>
       <c r="B1419" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1419" s="1" t="s">
-        <v>6845</v>
+        <v>6842</v>
       </c>
       <c r="D1419" s="1" t="s">
-        <v>6846</v>
+        <v>6843</v>
       </c>
       <c r="E1419" s="1" t="s">
-        <v>6847</v>
+        <v>6844</v>
       </c>
     </row>
     <row r="1420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1420" s="1" t="s">
-        <v>6848</v>
+        <v>6845</v>
       </c>
       <c r="B1420" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1420" s="1" t="s">
-        <v>6849</v>
+        <v>6846</v>
       </c>
       <c r="D1420" s="1"/>
       <c r="E1420" s="1" t="s">
-        <v>6850</v>
+        <v>6847</v>
       </c>
     </row>
     <row r="1421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1421" s="1" t="s">
-        <v>6851</v>
+        <v>6848</v>
       </c>
       <c r="B1421" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1421" s="1" t="s">
-        <v>6852</v>
+        <v>6849</v>
       </c>
       <c r="D1421" s="1"/>
       <c r="E1421" s="1" t="s">
-        <v>6853</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="1422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1422" s="1" t="s">
-        <v>6854</v>
+        <v>6851</v>
       </c>
       <c r="B1422" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1422" s="1" t="s">
-        <v>6855</v>
+        <v>6852</v>
       </c>
       <c r="D1422" s="1"/>
       <c r="E1422" s="1" t="s">
-        <v>6856</v>
+        <v>6853</v>
       </c>
     </row>
     <row r="1423" spans="1:5" x14ac:dyDescent="0.25">
@@ -53669,7 +53692,7 @@
         <v>6490</v>
       </c>
       <c r="E1647" s="1" t="s">
-        <v>6898</v>
+        <v>6895</v>
       </c>
     </row>
     <row r="1648" spans="1:5" x14ac:dyDescent="0.25">
@@ -58239,7 +58262,7 @@
         <v>3706</v>
       </c>
       <c r="E1920" s="1" t="s">
-        <v>6811</v>
+        <v>6808</v>
       </c>
     </row>
     <row r="1921" spans="1:5" x14ac:dyDescent="0.25">
@@ -60422,7 +60445,7 @@
         <v>1514</v>
       </c>
       <c r="E2050" s="1" t="s">
-        <v>6812</v>
+        <v>6809</v>
       </c>
     </row>
     <row r="2051" spans="1:5" x14ac:dyDescent="0.25">
@@ -61814,7 +61837,7 @@
         <v>6443</v>
       </c>
       <c r="E2134" s="1" t="s">
-        <v>6813</v>
+        <v>6810</v>
       </c>
     </row>
     <row r="2135" spans="1:5" x14ac:dyDescent="0.25">
@@ -62874,41 +62897,41 @@
     </row>
     <row r="2202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2202" s="1" t="s">
-        <v>6829</v>
+        <v>6826</v>
       </c>
       <c r="B2202" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2202" s="1" t="s">
-        <v>6830</v>
+        <v>6827</v>
       </c>
       <c r="E2202" s="1" t="s">
-        <v>6831</v>
+        <v>6828</v>
       </c>
     </row>
     <row r="2203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2203" s="1" t="s">
-        <v>6857</v>
+        <v>6854</v>
       </c>
       <c r="B2203" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2203" s="1" t="s">
-        <v>6858</v>
+        <v>6855</v>
       </c>
       <c r="E2203" s="1" t="s">
-        <v>6859</v>
+        <v>6856</v>
       </c>
     </row>
     <row r="2204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2204" s="1" t="s">
-        <v>6860</v>
+        <v>6857</v>
       </c>
       <c r="B2204" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2204" s="1" t="s">
-        <v>6861</v>
+        <v>6858</v>
       </c>
       <c r="E2204" s="1" t="s">
         <v>6677</v>
@@ -62916,13 +62939,13 @@
     </row>
     <row r="2205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2205" s="1" t="s">
-        <v>6862</v>
+        <v>6859</v>
       </c>
       <c r="B2205" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2205" s="1" t="s">
-        <v>6863</v>
+        <v>6860</v>
       </c>
       <c r="E2205" s="1" t="s">
         <v>6703</v>
@@ -62930,137 +62953,137 @@
     </row>
     <row r="2206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2206" s="1" t="s">
-        <v>6864</v>
+        <v>6861</v>
       </c>
       <c r="B2206" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2206" s="1" t="s">
-        <v>6865</v>
+        <v>6862</v>
       </c>
       <c r="E2206" s="1" t="s">
-        <v>6866</v>
+        <v>6863</v>
       </c>
     </row>
     <row r="2207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2207" s="1" t="s">
-        <v>6867</v>
+        <v>6864</v>
       </c>
       <c r="B2207" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2207" s="1" t="s">
-        <v>6868</v>
+        <v>6865</v>
       </c>
       <c r="E2207" s="1" t="s">
-        <v>6869</v>
+        <v>6866</v>
       </c>
     </row>
     <row r="2208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2208" s="1" t="s">
-        <v>6870</v>
+        <v>6867</v>
       </c>
       <c r="B2208" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2208" s="1" t="s">
-        <v>6871</v>
+        <v>6868</v>
       </c>
       <c r="E2208" s="1" t="s">
-        <v>6872</v>
+        <v>6869</v>
       </c>
     </row>
     <row r="2209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2209" s="1" t="s">
-        <v>6873</v>
+        <v>6870</v>
       </c>
       <c r="B2209" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2209" s="1" t="s">
-        <v>6874</v>
+        <v>6871</v>
       </c>
       <c r="E2209" s="1" t="s">
-        <v>6875</v>
+        <v>6872</v>
       </c>
     </row>
     <row r="2210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2210" s="1" t="s">
-        <v>6876</v>
+        <v>6873</v>
       </c>
       <c r="B2210" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2210" s="1" t="s">
-        <v>6877</v>
+        <v>6874</v>
       </c>
       <c r="D2210" s="1" t="s">
-        <v>6878</v>
+        <v>6875</v>
       </c>
       <c r="E2210" s="1" t="s">
-        <v>6879</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="2211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2211" s="1" t="s">
-        <v>6884</v>
+        <v>6881</v>
       </c>
       <c r="B2211" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2211" s="1" t="s">
-        <v>6885</v>
+        <v>6882</v>
       </c>
       <c r="D2211" s="1" t="s">
-        <v>6886</v>
+        <v>6883</v>
       </c>
       <c r="E2211" s="1" t="s">
-        <v>6887</v>
+        <v>6884</v>
       </c>
     </row>
     <row r="2212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2212" s="1" t="s">
-        <v>6888</v>
+        <v>6885</v>
       </c>
       <c r="B2212" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2212" s="1" t="s">
-        <v>6889</v>
+        <v>6886</v>
       </c>
       <c r="D2212" s="1" t="s">
-        <v>6890</v>
+        <v>6887</v>
       </c>
       <c r="E2212" s="1" t="s">
-        <v>6891</v>
+        <v>6888</v>
       </c>
     </row>
     <row r="2213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2213" s="1" t="s">
-        <v>6892</v>
+        <v>6889</v>
       </c>
       <c r="B2213" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2213" s="1" t="s">
-        <v>6893</v>
+        <v>6890</v>
       </c>
       <c r="E2213" s="1" t="s">
-        <v>6894</v>
+        <v>6891</v>
       </c>
     </row>
     <row r="2214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2214" s="1" t="s">
-        <v>6895</v>
+        <v>6892</v>
       </c>
       <c r="B2214" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2214" s="1" t="s">
-        <v>6896</v>
+        <v>6893</v>
       </c>
       <c r="E2214" s="1" t="s">
-        <v>6897</v>
+        <v>6894</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/String.xlsx
+++ b/config/Excel/String.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E80208D-6FE0-4CD3-991A-6737F45DCF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F571A75-8AE7-43CF-98F9-21506AEBC7EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10417" uniqueCount="6904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10461" uniqueCount="6938">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -27016,6 +27016,108 @@
   <si>
     <t>放入素材後顯示成功率。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2227</t>
+  </si>
+  <si>
+    <t>成就</t>
+  </si>
+  <si>
+    <t>文字｜achievements.js achUnlock：成就達成的戰鬥日誌</t>
+  </si>
+  <si>
+    <t>{0}=代入參數：成就名稱</t>
+  </si>
+  <si>
+    <t>成就達成：{0}</t>
+  </si>
+  <si>
+    <t>2228</t>
+  </si>
+  <si>
+    <t>界面文字｜Esc 菜單的成就按鈕與成就頁標題（index.html game-menu-achv／achv-modal-title）</t>
+  </si>
+  <si>
+    <t>2229</t>
+  </si>
+  <si>
+    <t>界面文字｜成就頁上方的達成統計（ui-achievements.js render）</t>
+  </si>
+  <si>
+    <t>{0}=代入參數：已達成數；{1}=代入參數：成就總數</t>
+  </si>
+  <si>
+    <t>已達成 {0} / {1}</t>
+  </si>
+  <si>
+    <t>2230</t>
+  </si>
+  <si>
+    <t>界面文字｜成就頁篩選：全部（ui-achievements.js）</t>
+  </si>
+  <si>
+    <t>全部</t>
+  </si>
+  <si>
+    <t>2231</t>
+  </si>
+  <si>
+    <t>界面文字｜成就頁篩選：已達成（ui-achievements.js）</t>
+  </si>
+  <si>
+    <t>已達成</t>
+  </si>
+  <si>
+    <t>2232</t>
+  </si>
+  <si>
+    <t>界面文字｜成就頁篩選：未達成（ui-achievements.js）</t>
+  </si>
+  <si>
+    <t>未達成</t>
+  </si>
+  <si>
+    <t>2233</t>
+  </si>
+  <si>
+    <t>提示｜成就卡片已達成時的達成日期（ui-achievements.js）</t>
+  </si>
+  <si>
+    <t>{0}=代入參數：達成日期（本地日期字串）</t>
+  </si>
+  <si>
+    <t>達成於 {0}</t>
+  </si>
+  <si>
+    <t>2234</t>
+  </si>
+  <si>
+    <t>界面文字｜成就頁左上返回按鈕的無障礙名稱（index.html achv-modal-close）</t>
+  </si>
+  <si>
+    <t>返回菜單</t>
+  </si>
+  <si>
+    <t>2235</t>
+  </si>
+  <si>
+    <t>提示｜解鎖成就時畫面上方的浮動提示標題（ui-achievements.js toast）</t>
+  </si>
+  <si>
+    <t>成就達成</t>
+  </si>
+  <si>
+    <t>2236</t>
+  </si>
+  <si>
+    <t>提示｜成就卡片未達成時的進度（ui-achievements.js）</t>
+  </si>
+  <si>
+    <t>{0}=代入參數：目前進度；{1}=代入參數：目標</t>
+  </si>
+  <si>
+    <t>進度 {0} / {1}</t>
   </si>
 </sst>
 </file>
@@ -27341,7 +27443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2214"/>
+  <dimension ref="A1:G2224"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.7109375" style="1" customWidth="1"/>
@@ -63086,6 +63188,158 @@
         <v>6894</v>
       </c>
     </row>
+    <row r="2215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2215" s="1" t="s">
+        <v>6904</v>
+      </c>
+      <c r="B2215" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2215" s="1" t="s">
+        <v>6906</v>
+      </c>
+      <c r="D2215" s="1" t="s">
+        <v>6907</v>
+      </c>
+      <c r="E2215" s="1" t="s">
+        <v>6908</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2216" s="1" t="s">
+        <v>6909</v>
+      </c>
+      <c r="B2216" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2216" s="1" t="s">
+        <v>6910</v>
+      </c>
+      <c r="E2216" s="1" t="s">
+        <v>6905</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2217" s="1" t="s">
+        <v>6911</v>
+      </c>
+      <c r="B2217" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2217" s="1" t="s">
+        <v>6912</v>
+      </c>
+      <c r="D2217" s="1" t="s">
+        <v>6913</v>
+      </c>
+      <c r="E2217" s="1" t="s">
+        <v>6914</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2218" s="1" t="s">
+        <v>6915</v>
+      </c>
+      <c r="B2218" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2218" s="1" t="s">
+        <v>6916</v>
+      </c>
+      <c r="E2218" s="1" t="s">
+        <v>6917</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2219" s="1" t="s">
+        <v>6918</v>
+      </c>
+      <c r="B2219" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2219" s="1" t="s">
+        <v>6919</v>
+      </c>
+      <c r="E2219" s="1" t="s">
+        <v>6920</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2220" s="1" t="s">
+        <v>6921</v>
+      </c>
+      <c r="B2220" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2220" s="1" t="s">
+        <v>6922</v>
+      </c>
+      <c r="E2220" s="1" t="s">
+        <v>6923</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2221" s="1" t="s">
+        <v>6924</v>
+      </c>
+      <c r="B2221" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2221" s="1" t="s">
+        <v>6925</v>
+      </c>
+      <c r="D2221" s="1" t="s">
+        <v>6926</v>
+      </c>
+      <c r="E2221" s="1" t="s">
+        <v>6927</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2222" s="1" t="s">
+        <v>6928</v>
+      </c>
+      <c r="B2222" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2222" s="1" t="s">
+        <v>6929</v>
+      </c>
+      <c r="E2222" s="1" t="s">
+        <v>6930</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2223" s="1" t="s">
+        <v>6931</v>
+      </c>
+      <c r="B2223" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2223" s="1" t="s">
+        <v>6932</v>
+      </c>
+      <c r="E2223" s="1" t="s">
+        <v>6933</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2224" s="1" t="s">
+        <v>6934</v>
+      </c>
+      <c r="B2224" s="1" t="s">
+        <v>6905</v>
+      </c>
+      <c r="C2224" s="1" t="s">
+        <v>6935</v>
+      </c>
+      <c r="D2224" s="1" t="s">
+        <v>6936</v>
+      </c>
+      <c r="E2224" s="1" t="s">
+        <v>6937</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/Excel/String.xlsx
+++ b/config/Excel/String.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alway\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06E3391-B19E-4943-9A7D-388465BAB578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{471573A8-F90B-4C60-B44C-CD89D374F9AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10528" uniqueCount="6943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10540" uniqueCount="6952">
   <si>
     <t>編號</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -27440,6 +27440,33 @@
   </si>
   <si>
     <t>點擊放入神性之石&lt;br&gt;神性之石可增加成功率</t>
+  </si>
+  <si>
+    <t>2240</t>
+  </si>
+  <si>
+    <t>勾選文字｜勝利後自動挑戰下一層（index.html tw-auto-advance）</t>
+  </si>
+  <si>
+    <t>自動推進</t>
+  </si>
+  <si>
+    <t>2241</t>
+  </si>
+  <si>
+    <t>提示｜自動推進規則（index.html tw-auto-advance）</t>
+  </si>
+  <si>
+    <t>勝利後自動挑戰下一層 BOSS；連續挑戰同一層時不生效，包含最後一場。失敗、撤退、到達最高層或金幣不足時停止。</t>
+  </si>
+  <si>
+    <t>2242</t>
+  </si>
+  <si>
+    <t>按鈕｜自動推進結算期間停止接續（ui.js trm-stop-auto）</t>
+  </si>
+  <si>
+    <t>停止推進</t>
   </si>
 </sst>
 </file>
@@ -27765,7 +27792,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2227"/>
+  <dimension ref="A1:G2230"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -59917,3942 +59944,3987 @@
     </row>
     <row r="1988" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1988" s="1" t="s">
-        <v>6251</v>
+        <v>6943</v>
       </c>
       <c r="B1988" s="1" t="s">
-        <v>3851</v>
+        <v>226</v>
       </c>
       <c r="C1988" s="1" t="s">
-        <v>3824</v>
-      </c>
-      <c r="D1988" s="1" t="s">
-        <v>445</v>
-      </c>
+        <v>6944</v>
+      </c>
+      <c r="D1988" s="1"/>
       <c r="E1988" s="1" t="s">
-        <v>3825</v>
+        <v>6945</v>
       </c>
     </row>
     <row r="1989" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1989" s="1" t="s">
-        <v>6252</v>
+        <v>6946</v>
       </c>
       <c r="B1989" s="1" t="s">
-        <v>3851</v>
+        <v>226</v>
       </c>
       <c r="C1989" s="1" t="s">
-        <v>3826</v>
-      </c>
-      <c r="D1989" s="1" t="s">
-        <v>445</v>
-      </c>
+        <v>6947</v>
+      </c>
+      <c r="D1989" s="1"/>
       <c r="E1989" s="1" t="s">
-        <v>3827</v>
+        <v>6948</v>
       </c>
     </row>
     <row r="1990" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1990" s="1" t="s">
-        <v>6253</v>
+        <v>6949</v>
       </c>
       <c r="B1990" s="1" t="s">
-        <v>3851</v>
+        <v>226</v>
       </c>
       <c r="C1990" s="1" t="s">
-        <v>3828</v>
-      </c>
-      <c r="D1990" s="1" t="s">
-        <v>445</v>
-      </c>
+        <v>6950</v>
+      </c>
+      <c r="D1990" s="1"/>
       <c r="E1990" s="1" t="s">
-        <v>3829</v>
+        <v>6951</v>
       </c>
     </row>
     <row r="1991" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1991" s="1" t="s">
-        <v>6254</v>
+        <v>6251</v>
       </c>
       <c r="B1991" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1991" s="1" t="s">
-        <v>3830</v>
+        <v>3824</v>
       </c>
       <c r="D1991" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E1991" s="1" t="s">
-        <v>3831</v>
+        <v>3825</v>
       </c>
     </row>
     <row r="1992" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1992" s="1" t="s">
-        <v>6255</v>
+        <v>6252</v>
       </c>
       <c r="B1992" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1992" s="1" t="s">
-        <v>3832</v>
+        <v>3826</v>
       </c>
       <c r="D1992" s="1" t="s">
-        <v>2588</v>
+        <v>445</v>
       </c>
       <c r="E1992" s="1" t="s">
-        <v>3833</v>
+        <v>3827</v>
       </c>
     </row>
     <row r="1993" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1993" s="1" t="s">
-        <v>6256</v>
+        <v>6253</v>
       </c>
       <c r="B1993" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1993" s="1" t="s">
-        <v>3834</v>
+        <v>3828</v>
       </c>
       <c r="D1993" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E1993" s="1" t="s">
-        <v>3835</v>
+        <v>3829</v>
       </c>
     </row>
     <row r="1994" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1994" s="1" t="s">
-        <v>6257</v>
+        <v>6254</v>
       </c>
       <c r="B1994" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1994" s="1" t="s">
-        <v>3836</v>
+        <v>3830</v>
       </c>
       <c r="D1994" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E1994" s="1" t="s">
-        <v>3837</v>
+        <v>3831</v>
       </c>
     </row>
     <row r="1995" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1995" s="1" t="s">
-        <v>6258</v>
+        <v>6255</v>
       </c>
       <c r="B1995" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1995" s="1" t="s">
-        <v>3838</v>
+        <v>3832</v>
       </c>
       <c r="D1995" s="1" t="s">
-        <v>6259</v>
+        <v>2588</v>
       </c>
       <c r="E1995" s="1" t="s">
-        <v>3839</v>
+        <v>3833</v>
       </c>
     </row>
     <row r="1996" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1996" s="1" t="s">
-        <v>6260</v>
+        <v>6256</v>
       </c>
       <c r="B1996" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1996" s="1" t="s">
-        <v>3840</v>
+        <v>3834</v>
       </c>
       <c r="D1996" s="1" t="s">
-        <v>6261</v>
+        <v>445</v>
       </c>
       <c r="E1996" s="1" t="s">
-        <v>3841</v>
+        <v>3835</v>
       </c>
     </row>
     <row r="1997" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1997" s="1" t="s">
-        <v>6262</v>
+        <v>6257</v>
       </c>
       <c r="B1997" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1997" s="1" t="s">
-        <v>3842</v>
+        <v>3836</v>
       </c>
       <c r="D1997" s="1" t="s">
-        <v>3843</v>
+        <v>445</v>
       </c>
       <c r="E1997" s="1" t="s">
-        <v>3844</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="1998" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1998" s="1" t="s">
-        <v>6263</v>
+        <v>6258</v>
       </c>
       <c r="B1998" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1998" s="1" t="s">
-        <v>3845</v>
+        <v>3838</v>
       </c>
       <c r="D1998" s="1" t="s">
-        <v>445</v>
+        <v>6259</v>
       </c>
       <c r="E1998" s="1" t="s">
-        <v>3846</v>
+        <v>3839</v>
       </c>
     </row>
     <row r="1999" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1999" s="1" t="s">
-        <v>6264</v>
+        <v>6260</v>
       </c>
       <c r="B1999" s="1" t="s">
         <v>3851</v>
       </c>
       <c r="C1999" s="1" t="s">
-        <v>1449</v>
+        <v>3840</v>
       </c>
       <c r="D1999" s="1" t="s">
-        <v>445</v>
+        <v>6261</v>
       </c>
       <c r="E1999" s="1" t="s">
-        <v>3847</v>
+        <v>3841</v>
       </c>
     </row>
     <row r="2000" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2000" s="1" t="s">
-        <v>6265</v>
+        <v>6262</v>
       </c>
       <c r="B2000" s="1" t="s">
-        <v>213</v>
+        <v>3851</v>
       </c>
       <c r="C2000" s="1" t="s">
-        <v>3848</v>
+        <v>3842</v>
       </c>
       <c r="D2000" s="1" t="s">
-        <v>6266</v>
+        <v>3843</v>
       </c>
       <c r="E2000" s="1" t="s">
-        <v>3849</v>
+        <v>3844</v>
       </c>
     </row>
     <row r="2001" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2001" s="1" t="s">
-        <v>6267</v>
+        <v>6263</v>
       </c>
       <c r="B2001" s="1" t="s">
-        <v>213</v>
+        <v>3851</v>
       </c>
       <c r="C2001" s="1" t="s">
-        <v>3850</v>
+        <v>3845</v>
       </c>
       <c r="D2001" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2001" s="1" t="s">
-        <v>3851</v>
+        <v>3846</v>
       </c>
     </row>
     <row r="2002" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2002" s="1" t="s">
-        <v>6268</v>
+        <v>6264</v>
       </c>
       <c r="B2002" s="1" t="s">
-        <v>213</v>
+        <v>3851</v>
       </c>
       <c r="C2002" s="1" t="s">
-        <v>3852</v>
+        <v>1449</v>
       </c>
       <c r="D2002" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2002" s="1" t="s">
-        <v>3853</v>
+        <v>3847</v>
       </c>
     </row>
     <row r="2003" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2003" s="1" t="s">
-        <v>6269</v>
+        <v>6265</v>
       </c>
       <c r="B2003" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C2003" s="1" t="s">
-        <v>3854</v>
+        <v>3848</v>
       </c>
       <c r="D2003" s="1" t="s">
-        <v>6774</v>
+        <v>6266</v>
       </c>
       <c r="E2003" s="1" t="s">
-        <v>3855</v>
+        <v>3849</v>
       </c>
     </row>
     <row r="2004" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2004" s="1" t="s">
-        <v>6270</v>
+        <v>6267</v>
       </c>
       <c r="B2004" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C2004" s="1" t="s">
-        <v>3856</v>
+        <v>3850</v>
       </c>
       <c r="D2004" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2004" s="1" t="s">
-        <v>3857</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="2005" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2005" s="1" t="s">
-        <v>6271</v>
+        <v>6268</v>
       </c>
       <c r="B2005" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C2005" s="1" t="s">
-        <v>3856</v>
+        <v>3852</v>
       </c>
       <c r="D2005" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2005" s="1" t="s">
-        <v>3858</v>
+        <v>3853</v>
       </c>
     </row>
     <row r="2006" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2006" s="1" t="s">
-        <v>6272</v>
+        <v>6269</v>
       </c>
       <c r="B2006" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C2006" s="1" t="s">
-        <v>3859</v>
+        <v>3854</v>
       </c>
       <c r="D2006" s="1" t="s">
-        <v>445</v>
+        <v>6774</v>
       </c>
       <c r="E2006" s="1" t="s">
-        <v>3860</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="2007" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2007" s="1" t="s">
-        <v>6273</v>
+        <v>6270</v>
       </c>
       <c r="B2007" s="1" t="s">
         <v>213</v>
       </c>
       <c r="C2007" s="1" t="s">
-        <v>3861</v>
+        <v>3856</v>
       </c>
       <c r="D2007" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2007" s="1" t="s">
-        <v>3862</v>
+        <v>3857</v>
       </c>
     </row>
     <row r="2008" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2008" s="1" t="s">
-        <v>6274</v>
+        <v>6271</v>
       </c>
       <c r="B2008" s="1" t="s">
-        <v>3851</v>
+        <v>213</v>
       </c>
       <c r="C2008" s="1" t="s">
-        <v>3863</v>
+        <v>3856</v>
       </c>
       <c r="D2008" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2008" s="1" t="s">
-        <v>3864</v>
+        <v>3858</v>
       </c>
     </row>
     <row r="2009" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2009" s="1" t="s">
-        <v>6275</v>
+        <v>6272</v>
       </c>
       <c r="B2009" s="1" t="s">
-        <v>3851</v>
+        <v>213</v>
       </c>
       <c r="C2009" s="1" t="s">
-        <v>3865</v>
+        <v>3859</v>
       </c>
       <c r="D2009" s="1" t="s">
-        <v>6276</v>
+        <v>445</v>
       </c>
       <c r="E2009" s="1" t="s">
-        <v>3866</v>
+        <v>3860</v>
       </c>
     </row>
     <row r="2010" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2010" s="1" t="s">
-        <v>6277</v>
+        <v>6273</v>
       </c>
       <c r="B2010" s="1" t="s">
-        <v>4350</v>
+        <v>213</v>
       </c>
       <c r="C2010" s="1" t="s">
-        <v>3868</v>
+        <v>3861</v>
       </c>
       <c r="D2010" s="1" t="s">
-        <v>3869</v>
+        <v>445</v>
       </c>
       <c r="E2010" s="1" t="s">
-        <v>3870</v>
+        <v>3862</v>
       </c>
     </row>
     <row r="2011" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2011" s="1" t="s">
-        <v>6278</v>
+        <v>6274</v>
       </c>
       <c r="B2011" s="1" t="s">
-        <v>4350</v>
+        <v>3851</v>
       </c>
       <c r="C2011" s="1" t="s">
-        <v>3871</v>
+        <v>3863</v>
       </c>
       <c r="D2011" s="1" t="s">
-        <v>3872</v>
+        <v>445</v>
       </c>
       <c r="E2011" s="1" t="s">
-        <v>3873</v>
+        <v>3864</v>
       </c>
     </row>
     <row r="2012" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2012" s="1" t="s">
-        <v>6279</v>
+        <v>6275</v>
       </c>
       <c r="B2012" s="1" t="s">
-        <v>4350</v>
+        <v>3851</v>
       </c>
       <c r="C2012" s="1" t="s">
-        <v>3874</v>
+        <v>3865</v>
       </c>
       <c r="D2012" s="1" t="s">
-        <v>445</v>
+        <v>6276</v>
       </c>
       <c r="E2012" s="1" t="s">
-        <v>3875</v>
+        <v>3866</v>
       </c>
     </row>
     <row r="2013" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2013" s="1" t="s">
-        <v>6280</v>
+        <v>6277</v>
       </c>
       <c r="B2013" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2013" s="1" t="s">
-        <v>3874</v>
+        <v>3868</v>
       </c>
       <c r="D2013" s="1" t="s">
-        <v>4351</v>
+        <v>3869</v>
       </c>
       <c r="E2013" s="1" t="s">
-        <v>3876</v>
+        <v>3870</v>
       </c>
     </row>
     <row r="2014" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2014" s="1" t="s">
-        <v>6281</v>
+        <v>6278</v>
       </c>
       <c r="B2014" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2014" s="1" t="s">
-        <v>3877</v>
+        <v>3871</v>
       </c>
       <c r="D2014" s="1" t="s">
-        <v>4352</v>
+        <v>3872</v>
       </c>
       <c r="E2014" s="1" t="s">
-        <v>3878</v>
+        <v>3873</v>
       </c>
     </row>
     <row r="2015" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2015" s="1" t="s">
-        <v>6282</v>
+        <v>6279</v>
       </c>
       <c r="B2015" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2015" s="1" t="s">
-        <v>3879</v>
+        <v>3874</v>
       </c>
       <c r="D2015" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2015" s="1" t="s">
-        <v>3880</v>
+        <v>3875</v>
       </c>
     </row>
     <row r="2016" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2016" s="1" t="s">
-        <v>6283</v>
+        <v>6280</v>
       </c>
       <c r="B2016" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2016" s="1" t="s">
-        <v>3881</v>
+        <v>3874</v>
       </c>
       <c r="D2016" s="1" t="s">
-        <v>445</v>
+        <v>4351</v>
       </c>
       <c r="E2016" s="1" t="s">
-        <v>3882</v>
+        <v>3876</v>
       </c>
     </row>
     <row r="2017" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2017" s="1" t="s">
-        <v>6284</v>
+        <v>6281</v>
       </c>
       <c r="B2017" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2017" s="1" t="s">
-        <v>3883</v>
+        <v>3877</v>
       </c>
       <c r="D2017" s="1" t="s">
-        <v>445</v>
+        <v>4352</v>
       </c>
       <c r="E2017" s="1" t="s">
-        <v>3884</v>
+        <v>3878</v>
       </c>
     </row>
     <row r="2018" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2018" s="1" t="s">
-        <v>6285</v>
+        <v>6282</v>
       </c>
       <c r="B2018" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2018" s="1" t="s">
-        <v>3885</v>
+        <v>3879</v>
       </c>
       <c r="D2018" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2018" s="1" t="s">
-        <v>3886</v>
+        <v>3880</v>
       </c>
     </row>
     <row r="2019" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2019" s="1" t="s">
-        <v>6286</v>
+        <v>6283</v>
       </c>
       <c r="B2019" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2019" s="1" t="s">
-        <v>3887</v>
+        <v>3881</v>
       </c>
       <c r="D2019" s="1" t="s">
-        <v>3888</v>
+        <v>445</v>
       </c>
       <c r="E2019" s="1" t="s">
-        <v>3889</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="2020" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2020" s="1" t="s">
-        <v>6287</v>
+        <v>6284</v>
       </c>
       <c r="B2020" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2020" s="1" t="s">
-        <v>2846</v>
+        <v>3883</v>
       </c>
       <c r="D2020" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2020" s="1" t="s">
-        <v>2847</v>
+        <v>3884</v>
       </c>
     </row>
     <row r="2021" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2021" s="1" t="s">
-        <v>6288</v>
+        <v>6285</v>
       </c>
       <c r="B2021" s="1" t="s">
         <v>4350</v>
       </c>
       <c r="C2021" s="1" t="s">
-        <v>2848</v>
+        <v>3885</v>
       </c>
       <c r="D2021" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2021" s="1" t="s">
-        <v>2849</v>
+        <v>3886</v>
       </c>
     </row>
     <row r="2022" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2022" s="1" t="s">
-        <v>6289</v>
+        <v>6286</v>
       </c>
       <c r="B2022" s="1" t="s">
-        <v>3867</v>
+        <v>4350</v>
       </c>
       <c r="C2022" s="1" t="s">
-        <v>2850</v>
+        <v>3887</v>
       </c>
       <c r="D2022" s="1" t="s">
-        <v>445</v>
+        <v>3888</v>
       </c>
       <c r="E2022" s="1" t="s">
-        <v>2851</v>
+        <v>3889</v>
       </c>
     </row>
     <row r="2023" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2023" s="1" t="s">
-        <v>6290</v>
+        <v>6287</v>
       </c>
       <c r="B2023" s="1" t="s">
-        <v>3867</v>
+        <v>4350</v>
       </c>
       <c r="C2023" s="1" t="s">
-        <v>2852</v>
+        <v>2846</v>
       </c>
       <c r="D2023" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2023" s="1" t="s">
-        <v>2853</v>
+        <v>2847</v>
       </c>
     </row>
     <row r="2024" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2024" s="1" t="s">
-        <v>6291</v>
+        <v>6288</v>
       </c>
       <c r="B2024" s="1" t="s">
-        <v>3867</v>
+        <v>4350</v>
       </c>
       <c r="C2024" s="1" t="s">
-        <v>2854</v>
+        <v>2848</v>
       </c>
       <c r="D2024" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2024" s="1" t="s">
-        <v>2855</v>
+        <v>2849</v>
       </c>
     </row>
     <row r="2025" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2025" s="1" t="s">
-        <v>6292</v>
+        <v>6289</v>
       </c>
       <c r="B2025" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2025" s="1" t="s">
-        <v>383</v>
+        <v>2850</v>
       </c>
       <c r="D2025" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2025" s="1" t="s">
-        <v>384</v>
+        <v>2851</v>
       </c>
     </row>
     <row r="2026" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2026" s="1" t="s">
-        <v>6293</v>
+        <v>6290</v>
       </c>
       <c r="B2026" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2026" s="1" t="s">
-        <v>2856</v>
+        <v>2852</v>
       </c>
       <c r="D2026" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2026" s="1" t="s">
-        <v>2857</v>
+        <v>2853</v>
       </c>
     </row>
     <row r="2027" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2027" s="1" t="s">
-        <v>6294</v>
+        <v>6291</v>
       </c>
       <c r="B2027" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2027" s="1" t="s">
-        <v>3890</v>
+        <v>2854</v>
       </c>
       <c r="D2027" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2027" s="1" t="s">
-        <v>3891</v>
+        <v>2855</v>
       </c>
     </row>
     <row r="2028" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2028" s="1" t="s">
-        <v>6295</v>
+        <v>6292</v>
       </c>
       <c r="B2028" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2028" s="1" t="s">
-        <v>3892</v>
+        <v>383</v>
       </c>
       <c r="D2028" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2028" s="1" t="s">
-        <v>3893</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2029" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2029" s="1" t="s">
-        <v>6296</v>
+        <v>6293</v>
       </c>
       <c r="B2029" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2029" s="1" t="s">
-        <v>3894</v>
+        <v>2856</v>
       </c>
       <c r="D2029" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2029" s="1" t="s">
-        <v>3895</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="2030" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2030" s="1" t="s">
-        <v>6297</v>
+        <v>6294</v>
       </c>
       <c r="B2030" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2030" s="1" t="s">
-        <v>3896</v>
+        <v>3890</v>
       </c>
       <c r="D2030" s="1" t="s">
-        <v>6473</v>
+        <v>445</v>
       </c>
       <c r="E2030" s="1" t="s">
-        <v>3897</v>
+        <v>3891</v>
       </c>
     </row>
     <row r="2031" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2031" s="1" t="s">
-        <v>6298</v>
+        <v>6295</v>
       </c>
       <c r="B2031" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2031" s="1" t="s">
-        <v>3898</v>
+        <v>3892</v>
       </c>
       <c r="D2031" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2031" s="1" t="s">
-        <v>3899</v>
+        <v>3893</v>
       </c>
     </row>
     <row r="2032" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2032" s="1" t="s">
-        <v>6299</v>
+        <v>6296</v>
       </c>
       <c r="B2032" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2032" s="1" t="s">
-        <v>3900</v>
+        <v>3894</v>
       </c>
       <c r="D2032" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2032" s="1" t="s">
-        <v>3901</v>
+        <v>3895</v>
       </c>
     </row>
     <row r="2033" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2033" s="1" t="s">
-        <v>6300</v>
+        <v>6297</v>
       </c>
       <c r="B2033" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2033" s="1" t="s">
-        <v>3902</v>
+        <v>3896</v>
       </c>
       <c r="D2033" s="1" t="s">
-        <v>445</v>
+        <v>6473</v>
       </c>
       <c r="E2033" s="1" t="s">
-        <v>3903</v>
+        <v>3897</v>
       </c>
     </row>
     <row r="2034" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2034" s="1" t="s">
-        <v>6301</v>
+        <v>6298</v>
       </c>
       <c r="B2034" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2034" s="1" t="s">
-        <v>3904</v>
+        <v>3898</v>
       </c>
       <c r="D2034" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2034" s="1" t="s">
-        <v>3905</v>
+        <v>3899</v>
       </c>
     </row>
     <row r="2035" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2035" s="1" t="s">
-        <v>6302</v>
+        <v>6299</v>
       </c>
       <c r="B2035" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2035" s="1" t="s">
-        <v>3906</v>
+        <v>3900</v>
       </c>
       <c r="D2035" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2035" s="1" t="s">
-        <v>3907</v>
+        <v>3901</v>
       </c>
     </row>
     <row r="2036" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2036" s="1" t="s">
-        <v>6303</v>
+        <v>6300</v>
       </c>
       <c r="B2036" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2036" s="1" t="s">
-        <v>3908</v>
+        <v>3902</v>
+      </c>
+      <c r="D2036" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2036" s="1" t="s">
-        <v>3909</v>
+        <v>3903</v>
       </c>
     </row>
     <row r="2037" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2037" s="1" t="s">
-        <v>6304</v>
+        <v>6301</v>
       </c>
       <c r="B2037" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2037" s="1" t="s">
-        <v>3910</v>
+        <v>3904</v>
       </c>
       <c r="D2037" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2037" s="1" t="s">
-        <v>3911</v>
+        <v>3905</v>
       </c>
     </row>
     <row r="2038" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2038" s="1" t="s">
-        <v>6305</v>
+        <v>6302</v>
       </c>
       <c r="B2038" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2038" s="1" t="s">
-        <v>3912</v>
+        <v>3906</v>
+      </c>
+      <c r="D2038" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2038" s="1" t="s">
-        <v>3913</v>
+        <v>3907</v>
       </c>
     </row>
     <row r="2039" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2039" s="1" t="s">
-        <v>6306</v>
+        <v>6303</v>
       </c>
       <c r="B2039" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2039" s="1" t="s">
-        <v>3914</v>
+        <v>3908</v>
       </c>
       <c r="E2039" s="1" t="s">
-        <v>3915</v>
+        <v>3909</v>
       </c>
     </row>
     <row r="2040" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2040" s="1" t="s">
-        <v>6307</v>
+        <v>6304</v>
       </c>
       <c r="B2040" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2040" s="1" t="s">
-        <v>3916</v>
+        <v>3910</v>
+      </c>
+      <c r="D2040" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2040" s="1" t="s">
-        <v>3917</v>
+        <v>3911</v>
       </c>
     </row>
     <row r="2041" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2041" s="1" t="s">
-        <v>6308</v>
+        <v>6305</v>
       </c>
       <c r="B2041" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2041" s="1" t="s">
-        <v>3918</v>
+        <v>3912</v>
       </c>
       <c r="E2041" s="1" t="s">
-        <v>3919</v>
+        <v>3913</v>
       </c>
     </row>
     <row r="2042" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2042" s="1" t="s">
-        <v>6309</v>
+        <v>6306</v>
       </c>
       <c r="B2042" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2042" s="1" t="s">
-        <v>3920</v>
-      </c>
-      <c r="D2042" s="1" t="s">
-        <v>445</v>
+        <v>3914</v>
       </c>
       <c r="E2042" s="1" t="s">
-        <v>3921</v>
+        <v>3915</v>
       </c>
     </row>
     <row r="2043" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2043" s="1" t="s">
-        <v>6310</v>
+        <v>6307</v>
       </c>
       <c r="B2043" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2043" s="1" t="s">
-        <v>3922</v>
-      </c>
-      <c r="D2043" s="1" t="s">
-        <v>445</v>
+        <v>3916</v>
       </c>
       <c r="E2043" s="1" t="s">
-        <v>3923</v>
+        <v>3917</v>
       </c>
     </row>
     <row r="2044" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2044" s="1" t="s">
-        <v>6311</v>
+        <v>6308</v>
       </c>
       <c r="B2044" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2044" s="1" t="s">
-        <v>3924</v>
-      </c>
-      <c r="D2044" s="1" t="s">
-        <v>185</v>
+        <v>3918</v>
       </c>
       <c r="E2044" s="1" t="s">
-        <v>3925</v>
+        <v>3919</v>
       </c>
     </row>
     <row r="2045" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2045" s="1" t="s">
-        <v>6312</v>
+        <v>6309</v>
       </c>
       <c r="B2045" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2045" s="1" t="s">
-        <v>3926</v>
+        <v>3920</v>
       </c>
       <c r="D2045" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2045" s="1" t="s">
-        <v>3927</v>
+        <v>3921</v>
       </c>
     </row>
     <row r="2046" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2046" s="1" t="s">
-        <v>6313</v>
+        <v>6310</v>
       </c>
       <c r="B2046" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2046" s="1" t="s">
-        <v>3928</v>
+        <v>3922</v>
       </c>
       <c r="D2046" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2046" s="1" t="s">
-        <v>3929</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="2047" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2047" s="1" t="s">
-        <v>6314</v>
+        <v>6311</v>
       </c>
       <c r="B2047" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2047" s="1" t="s">
-        <v>3930</v>
+        <v>3924</v>
       </c>
       <c r="D2047" s="1" t="s">
-        <v>445</v>
+        <v>185</v>
       </c>
       <c r="E2047" s="1" t="s">
-        <v>3931</v>
+        <v>3925</v>
       </c>
     </row>
     <row r="2048" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2048" s="1" t="s">
-        <v>6315</v>
+        <v>6312</v>
       </c>
       <c r="B2048" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2048" s="1" t="s">
-        <v>3932</v>
+        <v>3926</v>
       </c>
       <c r="D2048" s="1" t="s">
-        <v>96</v>
+        <v>445</v>
       </c>
       <c r="E2048" s="1" t="s">
-        <v>3933</v>
+        <v>3927</v>
       </c>
     </row>
     <row r="2049" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2049" s="1" t="s">
-        <v>6316</v>
+        <v>6313</v>
       </c>
       <c r="B2049" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2049" s="1" t="s">
-        <v>3934</v>
+        <v>3928</v>
       </c>
       <c r="D2049" s="1" t="s">
-        <v>1506</v>
+        <v>445</v>
       </c>
       <c r="E2049" s="1" t="s">
-        <v>3935</v>
+        <v>3929</v>
       </c>
     </row>
     <row r="2050" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2050" s="1" t="s">
-        <v>6317</v>
+        <v>6314</v>
       </c>
       <c r="B2050" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2050" s="1" t="s">
-        <v>3936</v>
+        <v>3930</v>
       </c>
       <c r="D2050" s="1" t="s">
-        <v>1506</v>
+        <v>445</v>
       </c>
       <c r="E2050" s="1" t="s">
-        <v>3937</v>
+        <v>3931</v>
       </c>
     </row>
     <row r="2051" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2051" s="1" t="s">
-        <v>6318</v>
+        <v>6315</v>
       </c>
       <c r="B2051" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2051" s="1" t="s">
-        <v>3938</v>
+        <v>3932</v>
       </c>
       <c r="D2051" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E2051" s="1" t="s">
-        <v>3939</v>
+        <v>3933</v>
       </c>
     </row>
     <row r="2052" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2052" s="1" t="s">
-        <v>6319</v>
+        <v>6316</v>
       </c>
       <c r="B2052" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2052" s="1" t="s">
-        <v>3940</v>
+        <v>3934</v>
       </c>
       <c r="D2052" s="1" t="s">
-        <v>96</v>
+        <v>1506</v>
       </c>
       <c r="E2052" s="1" t="s">
-        <v>6567</v>
+        <v>3935</v>
       </c>
     </row>
     <row r="2053" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2053" s="1" t="s">
-        <v>6320</v>
+        <v>6317</v>
       </c>
       <c r="B2053" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2053" s="1" t="s">
-        <v>3941</v>
+        <v>3936</v>
       </c>
       <c r="D2053" s="1" t="s">
         <v>1506</v>
       </c>
       <c r="E2053" s="1" t="s">
-        <v>3942</v>
+        <v>3937</v>
       </c>
     </row>
     <row r="2054" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2054" s="1" t="s">
-        <v>6321</v>
+        <v>6318</v>
       </c>
       <c r="B2054" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2054" s="1" t="s">
-        <v>3943</v>
+        <v>3938</v>
       </c>
       <c r="D2054" s="1" t="s">
-        <v>1506</v>
+        <v>96</v>
       </c>
       <c r="E2054" s="1" t="s">
-        <v>3944</v>
+        <v>3939</v>
       </c>
     </row>
     <row r="2055" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2055" s="1" t="s">
-        <v>6322</v>
+        <v>6319</v>
       </c>
       <c r="B2055" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2055" s="1" t="s">
-        <v>3945</v>
+        <v>3940</v>
       </c>
       <c r="D2055" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E2055" s="1" t="s">
-        <v>3946</v>
+        <v>6567</v>
       </c>
     </row>
     <row r="2056" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2056" s="1" t="s">
-        <v>6323</v>
+        <v>6320</v>
       </c>
       <c r="B2056" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2056" s="1" t="s">
-        <v>3947</v>
+        <v>3941</v>
       </c>
       <c r="D2056" s="1" t="s">
         <v>1506</v>
       </c>
       <c r="E2056" s="1" t="s">
-        <v>3948</v>
+        <v>3942</v>
       </c>
     </row>
     <row r="2057" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2057" s="1" t="s">
-        <v>6324</v>
+        <v>6321</v>
       </c>
       <c r="B2057" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2057" s="1" t="s">
-        <v>3949</v>
+        <v>3943</v>
       </c>
       <c r="D2057" s="1" t="s">
         <v>1506</v>
       </c>
       <c r="E2057" s="1" t="s">
-        <v>3950</v>
+        <v>3944</v>
       </c>
     </row>
     <row r="2058" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2058" s="1" t="s">
-        <v>6325</v>
+        <v>6322</v>
       </c>
       <c r="B2058" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2058" s="1" t="s">
-        <v>3951</v>
+        <v>3945</v>
       </c>
       <c r="D2058" s="1" t="s">
-        <v>1506</v>
+        <v>96</v>
       </c>
       <c r="E2058" s="1" t="s">
-        <v>6326</v>
+        <v>3946</v>
       </c>
     </row>
     <row r="2059" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2059" s="1" t="s">
-        <v>6327</v>
+        <v>6323</v>
       </c>
       <c r="B2059" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2059" s="1" t="s">
-        <v>3952</v>
+        <v>3947</v>
       </c>
       <c r="D2059" s="1" t="s">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="E2059" s="1" t="s">
-        <v>3953</v>
+        <v>3948</v>
       </c>
     </row>
     <row r="2060" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2060" s="1" t="s">
-        <v>6328</v>
+        <v>6324</v>
       </c>
       <c r="B2060" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2060" s="1" t="s">
-        <v>3954</v>
+        <v>3949</v>
       </c>
       <c r="D2060" s="1" t="s">
-        <v>3955</v>
+        <v>1506</v>
       </c>
       <c r="E2060" s="1" t="s">
-        <v>3956</v>
+        <v>3950</v>
       </c>
     </row>
     <row r="2061" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2061" s="1" t="s">
-        <v>6329</v>
+        <v>6325</v>
       </c>
       <c r="B2061" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2061" s="1" t="s">
-        <v>3957</v>
+        <v>3951</v>
       </c>
       <c r="D2061" s="1" t="s">
-        <v>445</v>
+        <v>1506</v>
       </c>
       <c r="E2061" s="1" t="s">
-        <v>3958</v>
+        <v>6326</v>
       </c>
     </row>
     <row r="2062" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2062" s="1" t="s">
-        <v>6330</v>
+        <v>6327</v>
       </c>
       <c r="B2062" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2062" s="1" t="s">
-        <v>3959</v>
+        <v>3952</v>
       </c>
       <c r="D2062" s="1" t="s">
-        <v>6331</v>
+        <v>445</v>
       </c>
       <c r="E2062" s="1" t="s">
-        <v>3960</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="2063" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2063" s="1" t="s">
-        <v>6332</v>
+        <v>6328</v>
       </c>
       <c r="B2063" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2063" s="1" t="s">
-        <v>3961</v>
+        <v>3954</v>
       </c>
       <c r="D2063" s="1" t="s">
-        <v>445</v>
+        <v>3955</v>
       </c>
       <c r="E2063" s="1" t="s">
-        <v>3962</v>
+        <v>3956</v>
       </c>
     </row>
     <row r="2064" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2064" s="1" t="s">
-        <v>6333</v>
+        <v>6329</v>
       </c>
       <c r="B2064" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2064" s="1" t="s">
-        <v>3961</v>
+        <v>3957</v>
+      </c>
+      <c r="D2064" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2064" s="1" t="s">
-        <v>3963</v>
+        <v>3958</v>
       </c>
     </row>
     <row r="2065" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2065" s="1" t="s">
-        <v>6334</v>
+        <v>6330</v>
       </c>
       <c r="B2065" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2065" s="1" t="s">
-        <v>3964</v>
+        <v>3959</v>
       </c>
       <c r="D2065" s="1" t="s">
-        <v>445</v>
+        <v>6331</v>
       </c>
       <c r="E2065" s="1" t="s">
-        <v>3965</v>
+        <v>3960</v>
       </c>
     </row>
     <row r="2066" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2066" s="1" t="s">
-        <v>6335</v>
+        <v>6332</v>
       </c>
       <c r="B2066" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2066" s="1" t="s">
-        <v>3966</v>
+        <v>3961</v>
       </c>
       <c r="D2066" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2066" s="1" t="s">
-        <v>3967</v>
+        <v>3962</v>
       </c>
     </row>
     <row r="2067" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2067" s="1" t="s">
-        <v>6336</v>
+        <v>6333</v>
       </c>
       <c r="B2067" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2067" s="1" t="s">
-        <v>3968</v>
-      </c>
-      <c r="D2067" s="1" t="s">
-        <v>6474</v>
+        <v>3961</v>
       </c>
       <c r="E2067" s="1" t="s">
-        <v>3969</v>
+        <v>3963</v>
       </c>
     </row>
     <row r="2068" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2068" s="1" t="s">
-        <v>6337</v>
+        <v>6334</v>
       </c>
       <c r="B2068" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2068" s="1" t="s">
-        <v>3970</v>
+        <v>3964</v>
       </c>
       <c r="D2068" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2068" s="1" t="s">
-        <v>3971</v>
+        <v>3965</v>
       </c>
     </row>
     <row r="2069" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2069" s="1" t="s">
-        <v>6338</v>
+        <v>6335</v>
       </c>
       <c r="B2069" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2069" s="1" t="s">
-        <v>3972</v>
+        <v>3966</v>
       </c>
       <c r="D2069" s="1" t="s">
-        <v>6475</v>
+        <v>445</v>
       </c>
       <c r="E2069" s="1" t="s">
-        <v>3973</v>
+        <v>3967</v>
       </c>
     </row>
     <row r="2070" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2070" s="1" t="s">
-        <v>6339</v>
+        <v>6336</v>
       </c>
       <c r="B2070" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2070" s="1" t="s">
-        <v>3974</v>
+        <v>3968</v>
       </c>
       <c r="D2070" s="1" t="s">
-        <v>6476</v>
+        <v>6474</v>
       </c>
       <c r="E2070" s="1" t="s">
-        <v>3975</v>
+        <v>3969</v>
       </c>
     </row>
     <row r="2071" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2071" s="1" t="s">
-        <v>6340</v>
+        <v>6337</v>
       </c>
       <c r="B2071" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2071" s="1" t="s">
-        <v>3976</v>
+        <v>3970</v>
       </c>
       <c r="D2071" s="1" t="s">
-        <v>6477</v>
+        <v>445</v>
       </c>
       <c r="E2071" s="1" t="s">
-        <v>3977</v>
+        <v>3971</v>
       </c>
     </row>
     <row r="2072" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2072" s="1" t="s">
-        <v>6341</v>
+        <v>6338</v>
       </c>
       <c r="B2072" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2072" s="1" t="s">
-        <v>3978</v>
+        <v>3972</v>
       </c>
       <c r="D2072" s="1" t="s">
-        <v>3979</v>
+        <v>6475</v>
       </c>
       <c r="E2072" s="1" t="s">
-        <v>3980</v>
+        <v>3973</v>
       </c>
     </row>
     <row r="2073" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2073" s="1" t="s">
-        <v>6342</v>
+        <v>6339</v>
       </c>
       <c r="B2073" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2073" s="1" t="s">
-        <v>3981</v>
+        <v>3974</v>
+      </c>
+      <c r="D2073" s="1" t="s">
+        <v>6476</v>
       </c>
       <c r="E2073" s="1" t="s">
-        <v>3982</v>
+        <v>3975</v>
       </c>
     </row>
     <row r="2074" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2074" s="1" t="s">
-        <v>6343</v>
+        <v>6340</v>
       </c>
       <c r="B2074" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2074" s="1" t="s">
-        <v>3983</v>
+        <v>3976</v>
       </c>
       <c r="D2074" s="1" t="s">
-        <v>445</v>
+        <v>6477</v>
       </c>
       <c r="E2074" s="1" t="s">
-        <v>3984</v>
+        <v>3977</v>
       </c>
     </row>
     <row r="2075" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2075" s="1" t="s">
-        <v>6344</v>
+        <v>6341</v>
       </c>
       <c r="B2075" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2075" s="1" t="s">
-        <v>3983</v>
+        <v>3978</v>
       </c>
       <c r="D2075" s="1" t="s">
-        <v>445</v>
+        <v>3979</v>
       </c>
       <c r="E2075" s="1" t="s">
-        <v>3985</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="2076" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2076" s="1" t="s">
-        <v>6345</v>
+        <v>6342</v>
       </c>
       <c r="B2076" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2076" s="1" t="s">
-        <v>3986</v>
-      </c>
-      <c r="D2076" s="1" t="s">
-        <v>445</v>
+        <v>3981</v>
       </c>
       <c r="E2076" s="1" t="s">
-        <v>3987</v>
+        <v>3982</v>
       </c>
     </row>
     <row r="2077" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2077" s="1" t="s">
-        <v>6346</v>
+        <v>6343</v>
       </c>
       <c r="B2077" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2077" s="1" t="s">
-        <v>3988</v>
+        <v>3983</v>
       </c>
       <c r="D2077" s="1" t="s">
-        <v>3989</v>
+        <v>445</v>
       </c>
       <c r="E2077" s="1" t="s">
-        <v>3990</v>
+        <v>3984</v>
       </c>
     </row>
     <row r="2078" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2078" s="1" t="s">
-        <v>6347</v>
+        <v>6344</v>
       </c>
       <c r="B2078" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2078" s="1" t="s">
-        <v>3991</v>
+        <v>3983</v>
       </c>
       <c r="D2078" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2078" s="1" t="s">
-        <v>3992</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="2079" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2079" s="1" t="s">
-        <v>6348</v>
+        <v>6345</v>
       </c>
       <c r="B2079" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2079" s="1" t="s">
-        <v>3993</v>
+        <v>3986</v>
       </c>
       <c r="D2079" s="1" t="s">
-        <v>6478</v>
+        <v>445</v>
       </c>
       <c r="E2079" s="1" t="s">
-        <v>3994</v>
+        <v>3987</v>
       </c>
     </row>
     <row r="2080" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2080" s="1" t="s">
-        <v>6349</v>
+        <v>6346</v>
       </c>
       <c r="B2080" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2080" s="1" t="s">
-        <v>3995</v>
+        <v>3988</v>
       </c>
       <c r="D2080" s="1" t="s">
-        <v>6350</v>
+        <v>3989</v>
       </c>
       <c r="E2080" s="1" t="s">
-        <v>3996</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="2081" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2081" s="1" t="s">
-        <v>6351</v>
+        <v>6347</v>
       </c>
       <c r="B2081" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2081" s="1" t="s">
-        <v>3997</v>
+        <v>3991</v>
       </c>
       <c r="D2081" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2081" s="1" t="s">
-        <v>3998</v>
+        <v>3992</v>
       </c>
     </row>
     <row r="2082" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2082" s="1" t="s">
-        <v>6352</v>
+        <v>6348</v>
       </c>
       <c r="B2082" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2082" s="1" t="s">
-        <v>3999</v>
+        <v>3993</v>
       </c>
       <c r="D2082" s="1" t="s">
-        <v>6353</v>
+        <v>6478</v>
       </c>
       <c r="E2082" s="1" t="s">
-        <v>4000</v>
+        <v>3994</v>
       </c>
     </row>
     <row r="2083" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2083" s="1" t="s">
-        <v>6354</v>
+        <v>6349</v>
       </c>
       <c r="B2083" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2083" s="1" t="s">
-        <v>4001</v>
+        <v>3995</v>
+      </c>
+      <c r="D2083" s="1" t="s">
+        <v>6350</v>
       </c>
       <c r="E2083" s="1" t="s">
-        <v>4002</v>
+        <v>3996</v>
       </c>
     </row>
     <row r="2084" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2084" s="1" t="s">
-        <v>6355</v>
+        <v>6351</v>
       </c>
       <c r="B2084" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2084" s="1" t="s">
-        <v>4003</v>
+        <v>3997</v>
       </c>
       <c r="D2084" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2084" s="1" t="s">
-        <v>4004</v>
+        <v>3998</v>
       </c>
     </row>
     <row r="2085" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2085" s="1" t="s">
-        <v>6356</v>
+        <v>6352</v>
       </c>
       <c r="B2085" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2085" s="1" t="s">
-        <v>4005</v>
+        <v>3999</v>
       </c>
       <c r="D2085" s="1" t="s">
-        <v>445</v>
+        <v>6353</v>
       </c>
       <c r="E2085" s="1" t="s">
-        <v>4006</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="2086" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2086" s="1" t="s">
-        <v>6357</v>
+        <v>6354</v>
       </c>
       <c r="B2086" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2086" s="1" t="s">
-        <v>4007</v>
-      </c>
-      <c r="D2086" s="1" t="s">
-        <v>445</v>
+        <v>4001</v>
       </c>
       <c r="E2086" s="1" t="s">
-        <v>4008</v>
+        <v>4002</v>
       </c>
     </row>
     <row r="2087" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2087" s="1" t="s">
-        <v>6358</v>
+        <v>6355</v>
       </c>
       <c r="B2087" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2087" s="1" t="s">
-        <v>4007</v>
+        <v>4003</v>
       </c>
       <c r="D2087" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2087" s="1" t="s">
-        <v>4009</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="2088" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2088" s="1" t="s">
-        <v>6359</v>
+        <v>6356</v>
       </c>
       <c r="B2088" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2088" s="1" t="s">
-        <v>4010</v>
+        <v>4005</v>
       </c>
       <c r="D2088" s="1" t="s">
-        <v>4011</v>
+        <v>445</v>
       </c>
       <c r="E2088" s="1" t="s">
-        <v>4012</v>
+        <v>4006</v>
       </c>
     </row>
     <row r="2089" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2089" s="1" t="s">
-        <v>6360</v>
+        <v>6357</v>
       </c>
       <c r="B2089" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2089" s="1" t="s">
-        <v>4013</v>
+        <v>4007</v>
       </c>
       <c r="D2089" s="1" t="s">
-        <v>4014</v>
+        <v>445</v>
       </c>
       <c r="E2089" s="1" t="s">
-        <v>4015</v>
+        <v>4008</v>
       </c>
     </row>
     <row r="2090" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2090" s="1" t="s">
-        <v>6361</v>
+        <v>6358</v>
       </c>
       <c r="B2090" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2090" s="1" t="s">
-        <v>4016</v>
+        <v>4007</v>
       </c>
       <c r="D2090" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2090" s="1" t="s">
-        <v>4017</v>
+        <v>4009</v>
       </c>
     </row>
     <row r="2091" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2091" s="1" t="s">
-        <v>6362</v>
+        <v>6359</v>
       </c>
       <c r="B2091" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2091" s="1" t="s">
-        <v>4018</v>
+        <v>4010</v>
+      </c>
+      <c r="D2091" s="1" t="s">
+        <v>4011</v>
       </c>
       <c r="E2091" s="1" t="s">
-        <v>4019</v>
+        <v>4012</v>
       </c>
     </row>
     <row r="2092" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2092" s="1" t="s">
-        <v>6363</v>
+        <v>6360</v>
       </c>
       <c r="B2092" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2092" s="1" t="s">
-        <v>4020</v>
+        <v>4013</v>
       </c>
       <c r="D2092" s="1" t="s">
-        <v>445</v>
+        <v>4014</v>
       </c>
       <c r="E2092" s="1" t="s">
-        <v>4021</v>
+        <v>4015</v>
       </c>
     </row>
     <row r="2093" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2093" s="1" t="s">
-        <v>6364</v>
+        <v>6361</v>
       </c>
       <c r="B2093" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2093" s="1" t="s">
-        <v>4022</v>
+        <v>4016</v>
       </c>
       <c r="D2093" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2093" s="1" t="s">
-        <v>4023</v>
+        <v>4017</v>
       </c>
     </row>
     <row r="2094" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2094" s="1" t="s">
-        <v>6365</v>
+        <v>6362</v>
       </c>
       <c r="B2094" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2094" s="1" t="s">
-        <v>4024</v>
-      </c>
-      <c r="D2094" s="1" t="s">
-        <v>445</v>
+        <v>4018</v>
       </c>
       <c r="E2094" s="1" t="s">
-        <v>4025</v>
+        <v>4019</v>
       </c>
     </row>
     <row r="2095" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2095" s="1" t="s">
-        <v>6366</v>
+        <v>6363</v>
       </c>
       <c r="B2095" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2095" s="1" t="s">
-        <v>4026</v>
+        <v>4020</v>
+      </c>
+      <c r="D2095" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2095" s="1" t="s">
-        <v>4027</v>
+        <v>4021</v>
       </c>
     </row>
     <row r="2096" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2096" s="1" t="s">
-        <v>6367</v>
+        <v>6364</v>
       </c>
       <c r="B2096" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2096" s="1" t="s">
-        <v>4026</v>
+        <v>4022</v>
       </c>
       <c r="D2096" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2096" s="1" t="s">
-        <v>4028</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="2097" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2097" s="1" t="s">
-        <v>6368</v>
+        <v>6365</v>
       </c>
       <c r="B2097" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2097" s="1" t="s">
-        <v>4029</v>
+        <v>4024</v>
+      </c>
+      <c r="D2097" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2097" s="1" t="s">
-        <v>4030</v>
+        <v>4025</v>
       </c>
     </row>
     <row r="2098" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2098" s="1" t="s">
-        <v>6369</v>
+        <v>6366</v>
       </c>
       <c r="B2098" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2098" s="1" t="s">
-        <v>4029</v>
-      </c>
-      <c r="D2098" s="1" t="s">
-        <v>445</v>
+        <v>4026</v>
       </c>
       <c r="E2098" s="1" t="s">
-        <v>4031</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="2099" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2099" s="1" t="s">
-        <v>6370</v>
+        <v>6367</v>
       </c>
       <c r="B2099" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2099" s="1" t="s">
-        <v>4032</v>
+        <v>4026</v>
       </c>
       <c r="D2099" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2099" s="1" t="s">
-        <v>4033</v>
+        <v>4028</v>
       </c>
     </row>
     <row r="2100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2100" s="1" t="s">
-        <v>6371</v>
+        <v>6368</v>
       </c>
       <c r="B2100" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2100" s="1" t="s">
-        <v>4034</v>
-      </c>
-      <c r="D2100" s="1" t="s">
-        <v>445</v>
+        <v>4029</v>
       </c>
       <c r="E2100" s="1" t="s">
-        <v>4035</v>
+        <v>4030</v>
       </c>
     </row>
     <row r="2101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2101" s="1" t="s">
-        <v>6372</v>
+        <v>6369</v>
       </c>
       <c r="B2101" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2101" s="1" t="s">
-        <v>4036</v>
+        <v>4029</v>
       </c>
       <c r="D2101" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2101" s="1" t="s">
-        <v>4037</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="2102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2102" s="1" t="s">
-        <v>6373</v>
+        <v>6370</v>
       </c>
       <c r="B2102" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2102" s="1" t="s">
-        <v>4038</v>
+        <v>4032</v>
       </c>
       <c r="D2102" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2102" s="1" t="s">
-        <v>4039</v>
+        <v>4033</v>
       </c>
     </row>
     <row r="2103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2103" s="1" t="s">
-        <v>6374</v>
+        <v>6371</v>
       </c>
       <c r="B2103" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2103" s="1" t="s">
-        <v>4040</v>
+        <v>4034</v>
       </c>
       <c r="D2103" s="1" t="s">
-        <v>6375</v>
+        <v>445</v>
       </c>
       <c r="E2103" s="1" t="s">
-        <v>4041</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="2104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2104" s="1" t="s">
-        <v>6376</v>
+        <v>6372</v>
       </c>
       <c r="B2104" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2104" s="1" t="s">
-        <v>4042</v>
+        <v>4036</v>
       </c>
       <c r="D2104" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2104" s="1" t="s">
-        <v>4043</v>
+        <v>4037</v>
       </c>
     </row>
     <row r="2105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2105" s="1" t="s">
-        <v>6377</v>
+        <v>6373</v>
       </c>
       <c r="B2105" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2105" s="1" t="s">
-        <v>4044</v>
+        <v>4038</v>
       </c>
       <c r="D2105" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2105" s="1" t="s">
-        <v>4045</v>
+        <v>4039</v>
       </c>
     </row>
     <row r="2106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2106" s="1" t="s">
-        <v>6378</v>
+        <v>6374</v>
       </c>
       <c r="B2106" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2106" s="1" t="s">
-        <v>4046</v>
+        <v>4040</v>
       </c>
       <c r="D2106" s="1" t="s">
-        <v>445</v>
+        <v>6375</v>
       </c>
       <c r="E2106" s="1" t="s">
-        <v>4047</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="2107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2107" s="1" t="s">
-        <v>6379</v>
+        <v>6376</v>
       </c>
       <c r="B2107" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2107" s="1" t="s">
-        <v>4048</v>
+        <v>4042</v>
       </c>
       <c r="D2107" s="1" t="s">
-        <v>6775</v>
+        <v>445</v>
       </c>
       <c r="E2107" s="1" t="s">
-        <v>4049</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="2108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2108" s="1" t="s">
-        <v>6380</v>
+        <v>6377</v>
       </c>
       <c r="B2108" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2108" s="1" t="s">
-        <v>4050</v>
+        <v>4044</v>
       </c>
       <c r="D2108" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2108" s="1" t="s">
-        <v>4051</v>
+        <v>4045</v>
       </c>
     </row>
     <row r="2109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2109" s="1" t="s">
-        <v>6381</v>
+        <v>6378</v>
       </c>
       <c r="B2109" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2109" s="1" t="s">
-        <v>4052</v>
+        <v>4046</v>
       </c>
       <c r="D2109" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2109" s="1" t="s">
-        <v>4053</v>
+        <v>4047</v>
       </c>
     </row>
     <row r="2110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2110" s="1" t="s">
-        <v>6382</v>
+        <v>6379</v>
       </c>
       <c r="B2110" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2110" s="1" t="s">
-        <v>4054</v>
+        <v>4048</v>
+      </c>
+      <c r="D2110" s="1" t="s">
+        <v>6775</v>
       </c>
       <c r="E2110" s="1" t="s">
-        <v>4055</v>
+        <v>4049</v>
       </c>
     </row>
     <row r="2111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2111" s="1" t="s">
-        <v>6383</v>
+        <v>6380</v>
       </c>
       <c r="B2111" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2111" s="1" t="s">
-        <v>4056</v>
+        <v>4050</v>
       </c>
       <c r="D2111" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2111" s="1" t="s">
-        <v>4057</v>
+        <v>4051</v>
       </c>
     </row>
     <row r="2112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2112" s="1" t="s">
-        <v>6384</v>
+        <v>6381</v>
       </c>
       <c r="B2112" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2112" s="1" t="s">
-        <v>4058</v>
+        <v>4052</v>
       </c>
       <c r="D2112" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2112" s="1" t="s">
-        <v>4059</v>
+        <v>4053</v>
       </c>
     </row>
     <row r="2113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2113" s="1" t="s">
-        <v>6385</v>
+        <v>6382</v>
       </c>
       <c r="B2113" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2113" s="1" t="s">
-        <v>4058</v>
+        <v>4054</v>
       </c>
       <c r="E2113" s="1" t="s">
-        <v>4060</v>
+        <v>4055</v>
       </c>
     </row>
     <row r="2114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2114" s="1" t="s">
-        <v>6386</v>
+        <v>6383</v>
       </c>
       <c r="B2114" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2114" s="1" t="s">
-        <v>4061</v>
+        <v>4056</v>
+      </c>
+      <c r="D2114" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2114" s="1" t="s">
-        <v>4062</v>
+        <v>4057</v>
       </c>
     </row>
     <row r="2115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2115" s="1" t="s">
-        <v>6387</v>
+        <v>6384</v>
       </c>
       <c r="B2115" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2115" s="1" t="s">
-        <v>4063</v>
+        <v>4058</v>
       </c>
       <c r="D2115" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2115" s="1" t="s">
-        <v>4064</v>
+        <v>4059</v>
       </c>
     </row>
     <row r="2116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2116" s="1" t="s">
-        <v>6388</v>
+        <v>6385</v>
       </c>
       <c r="B2116" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2116" s="1" t="s">
-        <v>4063</v>
-      </c>
-      <c r="D2116" s="1" t="s">
-        <v>445</v>
+        <v>4058</v>
       </c>
       <c r="E2116" s="1" t="s">
-        <v>4065</v>
+        <v>4060</v>
       </c>
     </row>
     <row r="2117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2117" s="1" t="s">
-        <v>6389</v>
+        <v>6386</v>
       </c>
       <c r="B2117" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2117" s="1" t="s">
-        <v>4066</v>
-      </c>
-      <c r="D2117" s="1" t="s">
-        <v>445</v>
+        <v>4061</v>
       </c>
       <c r="E2117" s="1" t="s">
-        <v>4067</v>
+        <v>4062</v>
       </c>
     </row>
     <row r="2118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2118" s="1" t="s">
-        <v>6390</v>
+        <v>6387</v>
       </c>
       <c r="B2118" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2118" s="1" t="s">
-        <v>4068</v>
+        <v>4063</v>
       </c>
       <c r="D2118" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2118" s="1" t="s">
-        <v>4069</v>
+        <v>4064</v>
       </c>
     </row>
     <row r="2119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2119" s="1" t="s">
-        <v>6391</v>
+        <v>6388</v>
       </c>
       <c r="B2119" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2119" s="1" t="s">
-        <v>4070</v>
+        <v>4063</v>
       </c>
       <c r="D2119" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2119" s="1" t="s">
-        <v>4071</v>
+        <v>4065</v>
       </c>
     </row>
     <row r="2120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2120" s="1" t="s">
-        <v>6392</v>
+        <v>6389</v>
       </c>
       <c r="B2120" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2120" s="1" t="s">
-        <v>4072</v>
+        <v>4066</v>
       </c>
       <c r="D2120" s="1" t="s">
-        <v>6479</v>
+        <v>445</v>
       </c>
       <c r="E2120" s="1" t="s">
-        <v>4073</v>
+        <v>4067</v>
       </c>
     </row>
     <row r="2121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2121" s="1" t="s">
-        <v>6393</v>
+        <v>6390</v>
       </c>
       <c r="B2121" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2121" s="1" t="s">
-        <v>4074</v>
+        <v>4068</v>
       </c>
       <c r="D2121" s="1" t="s">
-        <v>3869</v>
+        <v>445</v>
       </c>
       <c r="E2121" s="1" t="s">
-        <v>4075</v>
+        <v>4069</v>
       </c>
     </row>
     <row r="2122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2122" s="1" t="s">
-        <v>6394</v>
+        <v>6391</v>
       </c>
       <c r="B2122" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2122" s="1" t="s">
-        <v>4076</v>
+        <v>4070</v>
       </c>
       <c r="D2122" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2122" s="1" t="s">
-        <v>4077</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="2123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2123" s="1" t="s">
-        <v>6395</v>
+        <v>6392</v>
       </c>
       <c r="B2123" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2123" s="1" t="s">
-        <v>4078</v>
+        <v>4072</v>
       </c>
       <c r="D2123" s="1" t="s">
-        <v>6776</v>
+        <v>6479</v>
       </c>
       <c r="E2123" s="1" t="s">
-        <v>4079</v>
+        <v>4073</v>
       </c>
     </row>
     <row r="2124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2124" s="1" t="s">
-        <v>6396</v>
+        <v>6393</v>
       </c>
       <c r="B2124" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2124" s="1" t="s">
-        <v>4078</v>
+        <v>4074</v>
       </c>
       <c r="D2124" s="1" t="s">
-        <v>445</v>
+        <v>3869</v>
       </c>
       <c r="E2124" s="1" t="s">
-        <v>4080</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="2125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2125" s="1" t="s">
-        <v>6397</v>
+        <v>6394</v>
       </c>
       <c r="B2125" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2125" s="1" t="s">
-        <v>4078</v>
+        <v>4076</v>
       </c>
       <c r="D2125" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2125" s="1" t="s">
-        <v>4081</v>
+        <v>4077</v>
       </c>
     </row>
     <row r="2126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2126" s="1" t="s">
-        <v>6398</v>
+        <v>6395</v>
       </c>
       <c r="B2126" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2126" s="1" t="s">
-        <v>4082</v>
+        <v>4078</v>
       </c>
       <c r="D2126" s="1" t="s">
-        <v>6399</v>
+        <v>6776</v>
       </c>
       <c r="E2126" s="1" t="s">
-        <v>4083</v>
+        <v>4079</v>
       </c>
     </row>
     <row r="2127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2127" s="1" t="s">
-        <v>6400</v>
+        <v>6396</v>
       </c>
       <c r="B2127" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2127" s="1" t="s">
-        <v>6401</v>
+        <v>4078</v>
       </c>
       <c r="D2127" s="1" t="s">
-        <v>6777</v>
+        <v>445</v>
       </c>
       <c r="E2127" s="1" t="s">
-        <v>6402</v>
+        <v>4080</v>
       </c>
     </row>
     <row r="2128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2128" s="1" t="s">
-        <v>6403</v>
+        <v>6397</v>
       </c>
       <c r="B2128" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2128" s="1" t="s">
-        <v>4084</v>
+        <v>4078</v>
       </c>
       <c r="D2128" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2128" s="1" t="s">
-        <v>4085</v>
+        <v>4081</v>
       </c>
     </row>
     <row r="2129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2129" s="1" t="s">
-        <v>6404</v>
+        <v>6398</v>
       </c>
       <c r="B2129" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2129" s="1" t="s">
-        <v>4084</v>
+        <v>4082</v>
       </c>
       <c r="D2129" s="1" t="s">
-        <v>445</v>
+        <v>6399</v>
       </c>
       <c r="E2129" s="1" t="s">
-        <v>4086</v>
+        <v>4083</v>
       </c>
     </row>
     <row r="2130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2130" s="1" t="s">
-        <v>6405</v>
+        <v>6400</v>
       </c>
       <c r="B2130" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2130" s="1" t="s">
-        <v>4087</v>
+        <v>6401</v>
       </c>
       <c r="D2130" s="1" t="s">
-        <v>6480</v>
+        <v>6777</v>
       </c>
       <c r="E2130" s="1" t="s">
-        <v>4088</v>
+        <v>6402</v>
       </c>
     </row>
     <row r="2131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2131" s="1" t="s">
-        <v>6406</v>
+        <v>6403</v>
       </c>
       <c r="B2131" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2131" s="1" t="s">
-        <v>4089</v>
+        <v>4084</v>
       </c>
       <c r="D2131" s="1" t="s">
-        <v>6481</v>
+        <v>445</v>
       </c>
       <c r="E2131" s="1" t="s">
-        <v>4090</v>
+        <v>4085</v>
       </c>
     </row>
     <row r="2132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2132" s="1" t="s">
-        <v>6407</v>
+        <v>6404</v>
       </c>
       <c r="B2132" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2132" s="1" t="s">
-        <v>4091</v>
+        <v>4084</v>
       </c>
       <c r="D2132" s="1" t="s">
-        <v>4092</v>
+        <v>445</v>
       </c>
       <c r="E2132" s="1" t="s">
-        <v>4093</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="2133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2133" s="1" t="s">
-        <v>6408</v>
+        <v>6405</v>
       </c>
       <c r="B2133" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2133" s="1" t="s">
-        <v>4094</v>
+        <v>4087</v>
       </c>
       <c r="D2133" s="1" t="s">
-        <v>4095</v>
+        <v>6480</v>
       </c>
       <c r="E2133" s="1" t="s">
-        <v>4096</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="2134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2134" s="1" t="s">
-        <v>6409</v>
+        <v>6406</v>
       </c>
       <c r="B2134" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2134" s="1" t="s">
-        <v>4097</v>
+        <v>4089</v>
       </c>
       <c r="D2134" s="1" t="s">
-        <v>6482</v>
+        <v>6481</v>
       </c>
       <c r="E2134" s="1" t="s">
-        <v>4098</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="2135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2135" s="1" t="s">
-        <v>6410</v>
+        <v>6407</v>
       </c>
       <c r="B2135" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2135" s="1" t="s">
-        <v>4099</v>
+        <v>4091</v>
       </c>
       <c r="D2135" s="1" t="s">
-        <v>6411</v>
+        <v>4092</v>
       </c>
       <c r="E2135" s="1" t="s">
-        <v>4100</v>
+        <v>4093</v>
       </c>
     </row>
     <row r="2136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2136" s="1" t="s">
-        <v>6412</v>
+        <v>6408</v>
       </c>
       <c r="B2136" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2136" s="1" t="s">
-        <v>4101</v>
+        <v>4094</v>
       </c>
       <c r="D2136" s="1" t="s">
-        <v>6413</v>
+        <v>4095</v>
       </c>
       <c r="E2136" s="1" t="s">
-        <v>6568</v>
+        <v>4096</v>
       </c>
     </row>
     <row r="2137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2137" s="1" t="s">
-        <v>6414</v>
+        <v>6409</v>
       </c>
       <c r="B2137" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2137" s="1" t="s">
-        <v>4102</v>
+        <v>4097</v>
       </c>
       <c r="D2137" s="1" t="s">
-        <v>6415</v>
+        <v>6482</v>
       </c>
       <c r="E2137" s="1" t="s">
-        <v>4103</v>
+        <v>4098</v>
       </c>
     </row>
     <row r="2138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2138" s="1" t="s">
-        <v>6416</v>
+        <v>6410</v>
       </c>
       <c r="B2138" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2138" s="1" t="s">
-        <v>4104</v>
+        <v>4099</v>
       </c>
       <c r="D2138" s="1" t="s">
-        <v>3979</v>
+        <v>6411</v>
       </c>
       <c r="E2138" s="1" t="s">
-        <v>4105</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="2139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2139" s="1" t="s">
-        <v>6417</v>
+        <v>6412</v>
       </c>
       <c r="B2139" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2139" s="1" t="s">
-        <v>4106</v>
+        <v>4101</v>
       </c>
       <c r="D2139" s="1" t="s">
-        <v>445</v>
+        <v>6413</v>
       </c>
       <c r="E2139" s="1" t="s">
-        <v>4107</v>
+        <v>6568</v>
       </c>
     </row>
     <row r="2140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2140" s="1" t="s">
-        <v>6418</v>
+        <v>6414</v>
       </c>
       <c r="B2140" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2140" s="1" t="s">
-        <v>4108</v>
+        <v>4102</v>
       </c>
       <c r="D2140" s="1" t="s">
-        <v>445</v>
+        <v>6415</v>
       </c>
       <c r="E2140" s="1" t="s">
-        <v>4109</v>
+        <v>4103</v>
       </c>
     </row>
     <row r="2141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2141" s="1" t="s">
-        <v>6419</v>
+        <v>6416</v>
       </c>
       <c r="B2141" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2141" s="1" t="s">
-        <v>4110</v>
+        <v>4104</v>
       </c>
       <c r="D2141" s="1" t="s">
-        <v>445</v>
+        <v>3979</v>
       </c>
       <c r="E2141" s="1" t="s">
-        <v>4111</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="2142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2142" s="1" t="s">
-        <v>6420</v>
+        <v>6417</v>
       </c>
       <c r="B2142" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2142" s="1" t="s">
-        <v>4112</v>
+        <v>4106</v>
       </c>
       <c r="D2142" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2142" s="1" t="s">
-        <v>4113</v>
+        <v>4107</v>
       </c>
     </row>
     <row r="2143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2143" s="1" t="s">
-        <v>6421</v>
+        <v>6418</v>
       </c>
       <c r="B2143" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2143" s="1" t="s">
-        <v>4114</v>
+        <v>4108</v>
       </c>
       <c r="D2143" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2143" s="1" t="s">
-        <v>4115</v>
+        <v>4109</v>
       </c>
     </row>
     <row r="2144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2144" s="1" t="s">
-        <v>6422</v>
+        <v>6419</v>
       </c>
       <c r="B2144" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2144" s="1" t="s">
-        <v>4116</v>
+        <v>4110</v>
       </c>
       <c r="D2144" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2144" s="1" t="s">
-        <v>4117</v>
+        <v>4111</v>
       </c>
     </row>
     <row r="2145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2145" s="1" t="s">
-        <v>6423</v>
+        <v>6420</v>
       </c>
       <c r="B2145" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2145" s="1" t="s">
-        <v>4118</v>
+        <v>4112</v>
       </c>
       <c r="D2145" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2145" s="1" t="s">
-        <v>4119</v>
+        <v>4113</v>
       </c>
     </row>
     <row r="2146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2146" s="1" t="s">
-        <v>6424</v>
+        <v>6421</v>
       </c>
       <c r="B2146" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2146" s="1" t="s">
-        <v>4120</v>
+        <v>4114</v>
       </c>
       <c r="D2146" s="1" t="s">
-        <v>6778</v>
+        <v>445</v>
       </c>
       <c r="E2146" s="1" t="s">
-        <v>4121</v>
+        <v>4115</v>
       </c>
     </row>
     <row r="2147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2147" s="1" t="s">
-        <v>6425</v>
+        <v>6422</v>
       </c>
       <c r="B2147" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2147" s="1" t="s">
-        <v>4122</v>
+        <v>4116</v>
+      </c>
+      <c r="D2147" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2147" s="1" t="s">
-        <v>4123</v>
+        <v>4117</v>
       </c>
     </row>
     <row r="2148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2148" s="1" t="s">
-        <v>6426</v>
+        <v>6423</v>
       </c>
       <c r="B2148" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2148" s="1" t="s">
-        <v>4124</v>
+        <v>4118</v>
+      </c>
+      <c r="D2148" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2148" s="1" t="s">
-        <v>4125</v>
+        <v>4119</v>
       </c>
     </row>
     <row r="2149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2149" s="1" t="s">
-        <v>6427</v>
+        <v>6424</v>
       </c>
       <c r="B2149" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2149" s="1" t="s">
-        <v>4126</v>
+        <v>4120</v>
       </c>
       <c r="D2149" s="1" t="s">
-        <v>445</v>
+        <v>6778</v>
       </c>
       <c r="E2149" s="1" t="s">
-        <v>4127</v>
+        <v>4121</v>
       </c>
     </row>
     <row r="2150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2150" s="1" t="s">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="B2150" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2150" s="1" t="s">
-        <v>4128</v>
-      </c>
-      <c r="D2150" s="1" t="s">
-        <v>445</v>
+        <v>4122</v>
       </c>
       <c r="E2150" s="1" t="s">
-        <v>4129</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="2151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2151" s="1" t="s">
-        <v>6429</v>
+        <v>6426</v>
       </c>
       <c r="B2151" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2151" s="1" t="s">
-        <v>4130</v>
-      </c>
-      <c r="D2151" s="1" t="s">
-        <v>445</v>
+        <v>4124</v>
       </c>
       <c r="E2151" s="1" t="s">
-        <v>4131</v>
+        <v>4125</v>
       </c>
     </row>
     <row r="2152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2152" s="1" t="s">
-        <v>6430</v>
+        <v>6427</v>
       </c>
       <c r="B2152" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2152" s="1" t="s">
-        <v>4132</v>
+        <v>4126</v>
+      </c>
+      <c r="D2152" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2152" s="1" t="s">
-        <v>4133</v>
+        <v>4127</v>
       </c>
     </row>
     <row r="2153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2153" s="1" t="s">
-        <v>6431</v>
+        <v>6428</v>
       </c>
       <c r="B2153" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2153" s="1" t="s">
-        <v>4134</v>
+        <v>4128</v>
       </c>
       <c r="D2153" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2153" s="1" t="s">
-        <v>4135</v>
+        <v>4129</v>
       </c>
     </row>
     <row r="2154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2154" s="1" t="s">
-        <v>6432</v>
+        <v>6429</v>
       </c>
       <c r="B2154" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2154" s="1" t="s">
-        <v>4136</v>
+        <v>4130</v>
       </c>
       <c r="D2154" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2154" s="1" t="s">
-        <v>4137</v>
+        <v>4131</v>
       </c>
     </row>
     <row r="2155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2155" s="1" t="s">
-        <v>6433</v>
+        <v>6430</v>
       </c>
       <c r="B2155" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2155" s="1" t="s">
-        <v>4136</v>
-      </c>
-      <c r="D2155" s="1" t="s">
-        <v>6483</v>
+        <v>4132</v>
       </c>
       <c r="E2155" s="1" t="s">
-        <v>4138</v>
+        <v>4133</v>
       </c>
     </row>
     <row r="2156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2156" s="1" t="s">
-        <v>6434</v>
+        <v>6431</v>
       </c>
       <c r="B2156" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2156" s="1" t="s">
-        <v>4139</v>
+        <v>4134</v>
       </c>
       <c r="D2156" s="1" t="s">
-        <v>4140</v>
+        <v>445</v>
       </c>
       <c r="E2156" s="1" t="s">
-        <v>4141</v>
+        <v>4135</v>
       </c>
     </row>
     <row r="2157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2157" s="1" t="s">
-        <v>6435</v>
+        <v>6432</v>
       </c>
       <c r="B2157" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2157" s="1" t="s">
-        <v>4142</v>
+        <v>4136</v>
       </c>
       <c r="D2157" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2157" s="1" t="s">
-        <v>4143</v>
+        <v>4137</v>
       </c>
     </row>
     <row r="2158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2158" s="1" t="s">
-        <v>6436</v>
+        <v>6433</v>
       </c>
       <c r="B2158" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2158" s="1" t="s">
-        <v>4144</v>
+        <v>4136</v>
       </c>
       <c r="D2158" s="1" t="s">
-        <v>6484</v>
+        <v>6483</v>
       </c>
       <c r="E2158" s="1" t="s">
-        <v>4145</v>
+        <v>4138</v>
       </c>
     </row>
     <row r="2159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2159" s="1" t="s">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="B2159" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2159" s="1" t="s">
-        <v>4146</v>
+        <v>4139</v>
       </c>
       <c r="D2159" s="1" t="s">
-        <v>445</v>
+        <v>4140</v>
       </c>
       <c r="E2159" s="1" t="s">
-        <v>4147</v>
+        <v>4141</v>
       </c>
     </row>
     <row r="2160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2160" s="1" t="s">
-        <v>6438</v>
+        <v>6435</v>
       </c>
       <c r="B2160" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2160" s="1" t="s">
-        <v>4148</v>
+        <v>4142</v>
       </c>
       <c r="D2160" s="1" t="s">
-        <v>6779</v>
+        <v>445</v>
       </c>
       <c r="E2160" s="1" t="s">
-        <v>4149</v>
+        <v>4143</v>
       </c>
     </row>
     <row r="2161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2161" s="1" t="s">
-        <v>6439</v>
+        <v>6436</v>
       </c>
       <c r="B2161" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2161" s="1" t="s">
-        <v>4150</v>
+        <v>4144</v>
       </c>
       <c r="D2161" s="1" t="s">
-        <v>4151</v>
+        <v>6484</v>
       </c>
       <c r="E2161" s="1" t="s">
-        <v>4152</v>
+        <v>4145</v>
       </c>
     </row>
     <row r="2162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2162" s="1" t="s">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="B2162" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2162" s="1" t="s">
-        <v>4153</v>
+        <v>4146</v>
       </c>
       <c r="D2162" s="1" t="s">
-        <v>4154</v>
+        <v>445</v>
       </c>
       <c r="E2162" s="1" t="s">
-        <v>4155</v>
+        <v>4147</v>
       </c>
     </row>
     <row r="2163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2163" s="1" t="s">
-        <v>6441</v>
+        <v>6438</v>
       </c>
       <c r="B2163" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2163" s="1" t="s">
-        <v>4156</v>
+        <v>4148</v>
       </c>
       <c r="D2163" s="1" t="s">
-        <v>2601</v>
+        <v>6779</v>
       </c>
       <c r="E2163" s="1" t="s">
-        <v>4157</v>
+        <v>4149</v>
       </c>
     </row>
     <row r="2164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2164" s="1" t="s">
-        <v>6442</v>
+        <v>6439</v>
       </c>
       <c r="B2164" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2164" s="1" t="s">
-        <v>4158</v>
+        <v>4150</v>
       </c>
       <c r="D2164" s="1" t="s">
-        <v>445</v>
+        <v>4151</v>
       </c>
       <c r="E2164" s="1" t="s">
-        <v>4159</v>
+        <v>4152</v>
       </c>
     </row>
     <row r="2165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2165" s="1" t="s">
-        <v>6443</v>
+        <v>6440</v>
       </c>
       <c r="B2165" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2165" s="1" t="s">
-        <v>4160</v>
+        <v>4153</v>
       </c>
       <c r="D2165" s="1" t="s">
-        <v>445</v>
+        <v>4154</v>
       </c>
       <c r="E2165" s="1" t="s">
-        <v>4161</v>
+        <v>4155</v>
       </c>
     </row>
     <row r="2166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2166" s="1" t="s">
-        <v>6444</v>
+        <v>6441</v>
       </c>
       <c r="B2166" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2166" s="1" t="s">
-        <v>4162</v>
+        <v>4156</v>
       </c>
       <c r="D2166" s="1" t="s">
-        <v>4014</v>
+        <v>2601</v>
       </c>
       <c r="E2166" s="1" t="s">
-        <v>4163</v>
+        <v>4157</v>
       </c>
     </row>
     <row r="2167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2167" s="1" t="s">
-        <v>6445</v>
+        <v>6442</v>
       </c>
       <c r="B2167" s="1" t="s">
         <v>3867</v>
       </c>
       <c r="C2167" s="1" t="s">
-        <v>4164</v>
+        <v>4158</v>
       </c>
       <c r="D2167" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2167" s="1" t="s">
-        <v>4165</v>
+        <v>4159</v>
       </c>
     </row>
     <row r="2168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2168" s="1" t="s">
-        <v>6446</v>
+        <v>6443</v>
       </c>
       <c r="B2168" s="1" t="s">
-        <v>4350</v>
+        <v>3867</v>
       </c>
       <c r="C2168" s="1" t="s">
-        <v>4166</v>
+        <v>4160</v>
       </c>
       <c r="D2168" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2168" s="1" t="s">
-        <v>4167</v>
+        <v>4161</v>
       </c>
     </row>
     <row r="2169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2169" s="1" t="s">
-        <v>6447</v>
+        <v>6444</v>
       </c>
       <c r="B2169" s="1" t="s">
-        <v>4350</v>
+        <v>3867</v>
       </c>
       <c r="C2169" s="1" t="s">
-        <v>4168</v>
+        <v>4162</v>
       </c>
       <c r="D2169" s="1" t="s">
-        <v>445</v>
+        <v>4014</v>
       </c>
       <c r="E2169" s="1" t="s">
-        <v>4169</v>
+        <v>4163</v>
       </c>
     </row>
     <row r="2170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2170" s="1" t="s">
-        <v>6780</v>
+        <v>6445</v>
       </c>
       <c r="B2170" s="1" t="s">
-        <v>186</v>
+        <v>3867</v>
       </c>
       <c r="C2170" s="1" t="s">
-        <v>6781</v>
+        <v>4164</v>
       </c>
       <c r="D2170" s="1" t="s">
-        <v>6486</v>
+        <v>445</v>
       </c>
       <c r="E2170" s="1" t="s">
-        <v>6782</v>
+        <v>4165</v>
       </c>
     </row>
     <row r="2171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2171" s="1" t="s">
-        <v>6783</v>
+        <v>6446</v>
       </c>
       <c r="B2171" s="1" t="s">
-        <v>186</v>
+        <v>4350</v>
       </c>
       <c r="C2171" s="1" t="s">
-        <v>6784</v>
+        <v>4166</v>
       </c>
       <c r="D2171" s="1" t="s">
-        <v>6785</v>
+        <v>445</v>
       </c>
       <c r="E2171" s="1" t="s">
-        <v>6786</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="2172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2172" s="1" t="s">
-        <v>6787</v>
+        <v>6447</v>
       </c>
       <c r="B2172" s="1" t="s">
-        <v>186</v>
+        <v>4350</v>
       </c>
       <c r="C2172" s="1" t="s">
-        <v>6487</v>
+        <v>4168</v>
+      </c>
+      <c r="D2172" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2172" s="1" t="s">
-        <v>6788</v>
+        <v>4169</v>
       </c>
     </row>
     <row r="2173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2173" s="1" t="s">
-        <v>6789</v>
+        <v>6780</v>
       </c>
       <c r="B2173" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2173" s="1" t="s">
-        <v>6790</v>
+        <v>6781</v>
       </c>
       <c r="D2173" s="1" t="s">
-        <v>6488</v>
+        <v>6486</v>
       </c>
       <c r="E2173" s="1" t="s">
-        <v>6791</v>
+        <v>6782</v>
       </c>
     </row>
     <row r="2174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2174" s="1" t="s">
-        <v>6792</v>
+        <v>6783</v>
       </c>
       <c r="B2174" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2174" s="1" t="s">
-        <v>6790</v>
+        <v>6784</v>
+      </c>
+      <c r="D2174" s="1" t="s">
+        <v>6785</v>
       </c>
       <c r="E2174" s="1" t="s">
-        <v>6793</v>
+        <v>6786</v>
       </c>
     </row>
     <row r="2175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2175" s="1" t="s">
-        <v>6794</v>
+        <v>6787</v>
       </c>
       <c r="B2175" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2175" s="1" t="s">
-        <v>6795</v>
+        <v>6487</v>
       </c>
       <c r="E2175" s="1" t="s">
-        <v>6796</v>
+        <v>6788</v>
       </c>
     </row>
     <row r="2176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2176" s="1" t="s">
-        <v>6797</v>
+        <v>6789</v>
       </c>
       <c r="B2176" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2176" s="1" t="s">
-        <v>6798</v>
+        <v>6790</v>
       </c>
       <c r="D2176" s="1" t="s">
-        <v>445</v>
+        <v>6488</v>
       </c>
       <c r="E2176" s="1" t="s">
-        <v>6799</v>
+        <v>6791</v>
       </c>
     </row>
     <row r="2177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2177" s="1" t="s">
-        <v>6800</v>
+        <v>6792</v>
       </c>
       <c r="B2177" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2177" s="1" t="s">
-        <v>6801</v>
+        <v>6790</v>
       </c>
       <c r="E2177" s="1" t="s">
-        <v>6802</v>
+        <v>6793</v>
       </c>
     </row>
     <row r="2178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2178" s="1" t="s">
-        <v>6803</v>
+        <v>6794</v>
       </c>
       <c r="B2178" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2178" s="1" t="s">
-        <v>6804</v>
-      </c>
-      <c r="D2178" s="1" t="s">
-        <v>6489</v>
+        <v>6795</v>
       </c>
       <c r="E2178" s="1" t="s">
-        <v>6805</v>
+        <v>6796</v>
       </c>
     </row>
     <row r="2179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2179" s="1" t="s">
-        <v>6806</v>
+        <v>6797</v>
       </c>
       <c r="B2179" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2179" s="1" t="s">
-        <v>6807</v>
+        <v>6798</v>
       </c>
       <c r="D2179" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2179" s="1" t="s">
-        <v>6808</v>
+        <v>6799</v>
       </c>
     </row>
     <row r="2180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2180" s="1" t="s">
-        <v>6809</v>
+        <v>6800</v>
       </c>
       <c r="B2180" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2180" s="1" t="s">
-        <v>6810</v>
+        <v>6801</v>
       </c>
       <c r="E2180" s="1" t="s">
-        <v>6811</v>
+        <v>6802</v>
       </c>
     </row>
     <row r="2181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2181" s="1" t="s">
-        <v>6812</v>
+        <v>6803</v>
       </c>
       <c r="B2181" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2181" s="1" t="s">
-        <v>6813</v>
+        <v>6804</v>
       </c>
       <c r="D2181" s="1" t="s">
-        <v>6490</v>
+        <v>6489</v>
       </c>
       <c r="E2181" s="1" t="s">
-        <v>6814</v>
+        <v>6805</v>
       </c>
     </row>
     <row r="2182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2182" s="1" t="s">
-        <v>6815</v>
+        <v>6806</v>
       </c>
       <c r="B2182" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2182" s="1" t="s">
-        <v>6816</v>
+        <v>6807</v>
       </c>
       <c r="D2182" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2182" s="1" t="s">
-        <v>6817</v>
+        <v>6808</v>
       </c>
     </row>
     <row r="2183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2183" s="1" t="s">
-        <v>6818</v>
+        <v>6809</v>
       </c>
       <c r="B2183" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2183" s="1" t="s">
-        <v>6819</v>
+        <v>6810</v>
       </c>
       <c r="E2183" s="1" t="s">
-        <v>6820</v>
+        <v>6811</v>
       </c>
     </row>
     <row r="2184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2184" s="1" t="s">
-        <v>6821</v>
+        <v>6812</v>
       </c>
       <c r="B2184" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2184" s="1" t="s">
-        <v>6822</v>
+        <v>6813</v>
       </c>
       <c r="D2184" s="1" t="s">
-        <v>6491</v>
+        <v>6490</v>
       </c>
       <c r="E2184" s="1" t="s">
-        <v>6823</v>
+        <v>6814</v>
       </c>
     </row>
     <row r="2185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2185" s="1" t="s">
-        <v>6824</v>
+        <v>6815</v>
       </c>
       <c r="B2185" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2185" s="1" t="s">
-        <v>6822</v>
+        <v>6816</v>
+      </c>
+      <c r="D2185" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2185" s="1" t="s">
-        <v>6825</v>
+        <v>6817</v>
       </c>
     </row>
     <row r="2186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2186" s="1" t="s">
-        <v>6826</v>
+        <v>6818</v>
       </c>
       <c r="B2186" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2186" s="1" t="s">
-        <v>6827</v>
+        <v>6819</v>
       </c>
       <c r="E2186" s="1" t="s">
-        <v>6828</v>
+        <v>6820</v>
       </c>
     </row>
     <row r="2187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2187" s="1" t="s">
-        <v>6829</v>
+        <v>6821</v>
       </c>
       <c r="B2187" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2187" s="1" t="s">
-        <v>6830</v>
+        <v>6822</v>
       </c>
       <c r="D2187" s="1" t="s">
-        <v>445</v>
+        <v>6491</v>
       </c>
       <c r="E2187" s="1" t="s">
-        <v>6831</v>
+        <v>6823</v>
       </c>
     </row>
     <row r="2188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2188" s="1" t="s">
-        <v>6832</v>
+        <v>6824</v>
       </c>
       <c r="B2188" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2188" s="1" t="s">
-        <v>6833</v>
+        <v>6822</v>
       </c>
       <c r="E2188" s="1" t="s">
-        <v>6834</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="2189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2189" s="1" t="s">
-        <v>6835</v>
+        <v>6826</v>
       </c>
       <c r="B2189" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2189" s="1" t="s">
-        <v>6836</v>
-      </c>
-      <c r="D2189" s="1" t="s">
-        <v>6492</v>
+        <v>6827</v>
       </c>
       <c r="E2189" s="1" t="s">
-        <v>6837</v>
+        <v>6828</v>
       </c>
     </row>
     <row r="2190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2190" s="1" t="s">
-        <v>6838</v>
+        <v>6829</v>
       </c>
       <c r="B2190" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2190" s="1" t="s">
-        <v>6839</v>
+        <v>6830</v>
+      </c>
+      <c r="D2190" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2190" s="1" t="s">
-        <v>6840</v>
+        <v>6831</v>
       </c>
     </row>
     <row r="2191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2191" s="1" t="s">
-        <v>6841</v>
+        <v>6832</v>
       </c>
       <c r="B2191" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2191" s="1" t="s">
-        <v>6842</v>
-      </c>
-      <c r="D2191" s="1" t="s">
-        <v>445</v>
+        <v>6833</v>
       </c>
       <c r="E2191" s="1" t="s">
-        <v>6843</v>
+        <v>6834</v>
       </c>
     </row>
     <row r="2192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2192" s="1" t="s">
-        <v>6844</v>
+        <v>6835</v>
       </c>
       <c r="B2192" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2192" s="1" t="s">
-        <v>6845</v>
+        <v>6836</v>
+      </c>
+      <c r="D2192" s="1" t="s">
+        <v>6492</v>
       </c>
       <c r="E2192" s="1" t="s">
-        <v>6846</v>
+        <v>6837</v>
       </c>
     </row>
     <row r="2193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2193" s="1" t="s">
-        <v>6847</v>
+        <v>6838</v>
       </c>
       <c r="B2193" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2193" s="1" t="s">
-        <v>6795</v>
-      </c>
-      <c r="D2193" s="1" t="s">
-        <v>6491</v>
+        <v>6839</v>
       </c>
       <c r="E2193" s="1" t="s">
-        <v>6493</v>
+        <v>6840</v>
       </c>
     </row>
     <row r="2194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2194" s="1" t="s">
-        <v>6848</v>
+        <v>6841</v>
       </c>
       <c r="B2194" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2194" s="1" t="s">
-        <v>6849</v>
+        <v>6842</v>
+      </c>
+      <c r="D2194" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2194" s="1" t="s">
-        <v>6850</v>
+        <v>6843</v>
       </c>
     </row>
     <row r="2195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2195" s="1" t="s">
-        <v>6851</v>
+        <v>6844</v>
       </c>
       <c r="B2195" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2195" s="1" t="s">
-        <v>6852</v>
+        <v>6845</v>
       </c>
       <c r="E2195" s="1" t="s">
-        <v>6853</v>
+        <v>6846</v>
       </c>
     </row>
     <row r="2196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2196" s="1" t="s">
-        <v>6854</v>
+        <v>6847</v>
       </c>
       <c r="B2196" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2196" s="1" t="s">
-        <v>6855</v>
+        <v>6795</v>
+      </c>
+      <c r="D2196" s="1" t="s">
+        <v>6491</v>
       </c>
       <c r="E2196" s="1" t="s">
-        <v>6856</v>
+        <v>6493</v>
       </c>
     </row>
     <row r="2197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2197" s="1" t="s">
-        <v>6857</v>
+        <v>6848</v>
       </c>
       <c r="B2197" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2197" s="1" t="s">
-        <v>6858</v>
+        <v>6849</v>
       </c>
       <c r="E2197" s="1" t="s">
-        <v>6859</v>
+        <v>6850</v>
       </c>
     </row>
     <row r="2198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2198" s="1" t="s">
-        <v>6860</v>
+        <v>6851</v>
       </c>
       <c r="B2198" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2198" s="1" t="s">
-        <v>6861</v>
-      </c>
-      <c r="D2198" s="1" t="s">
-        <v>445</v>
+        <v>6852</v>
       </c>
       <c r="E2198" s="1" t="s">
-        <v>6862</v>
+        <v>6853</v>
       </c>
     </row>
     <row r="2199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2199" s="1" t="s">
-        <v>6863</v>
+        <v>6854</v>
       </c>
       <c r="B2199" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2199" s="1" t="s">
-        <v>6864</v>
-      </c>
-      <c r="D2199" s="1"/>
+        <v>6855</v>
+      </c>
       <c r="E2199" s="1" t="s">
-        <v>6865</v>
+        <v>6856</v>
       </c>
     </row>
     <row r="2200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2200" s="1" t="s">
-        <v>6523</v>
+        <v>6857</v>
       </c>
       <c r="B2200" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2200" s="1" t="s">
-        <v>6866</v>
-      </c>
-      <c r="D2200" s="1" t="s">
-        <v>6494</v>
+        <v>6858</v>
       </c>
       <c r="E2200" s="1" t="s">
-        <v>6867</v>
+        <v>6859</v>
       </c>
     </row>
     <row r="2201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2201" s="1" t="s">
-        <v>6868</v>
+        <v>6860</v>
       </c>
       <c r="B2201" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2201" s="1" t="s">
-        <v>6869</v>
-      </c>
-      <c r="D2201" s="1"/>
+        <v>6861</v>
+      </c>
+      <c r="D2201" s="1" t="s">
+        <v>445</v>
+      </c>
       <c r="E2201" s="1" t="s">
-        <v>6870</v>
+        <v>6862</v>
       </c>
     </row>
     <row r="2202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2202" s="1" t="s">
-        <v>6871</v>
+        <v>6863</v>
       </c>
       <c r="B2202" s="1" t="s">
         <v>186</v>
       </c>
       <c r="C2202" s="1" t="s">
-        <v>6872</v>
-      </c>
+        <v>6864</v>
+      </c>
+      <c r="D2202" s="1"/>
       <c r="E2202" s="1" t="s">
-        <v>6873</v>
+        <v>6865</v>
       </c>
     </row>
     <row r="2203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2203" s="1" t="s">
-        <v>6874</v>
+        <v>6523</v>
       </c>
       <c r="B2203" s="1" t="s">
-        <v>1399</v>
+        <v>186</v>
       </c>
       <c r="C2203" s="1" t="s">
-        <v>6875</v>
+        <v>6866</v>
+      </c>
+      <c r="D2203" s="1" t="s">
+        <v>6494</v>
       </c>
       <c r="E2203" s="1" t="s">
-        <v>6876</v>
+        <v>6867</v>
       </c>
     </row>
     <row r="2204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2204" s="1" t="s">
-        <v>6877</v>
+        <v>6868</v>
       </c>
       <c r="B2204" s="1" t="s">
-        <v>1399</v>
+        <v>186</v>
       </c>
       <c r="C2204" s="1" t="s">
-        <v>6878</v>
-      </c>
+        <v>6869</v>
+      </c>
+      <c r="D2204" s="1"/>
       <c r="E2204" s="1" t="s">
-        <v>6879</v>
+        <v>6870</v>
       </c>
     </row>
     <row r="2205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2205" s="1" t="s">
-        <v>6880</v>
+        <v>6871</v>
       </c>
       <c r="B2205" s="1" t="s">
-        <v>25</v>
+        <v>186</v>
       </c>
       <c r="C2205" s="1" t="s">
-        <v>6881</v>
+        <v>6872</v>
       </c>
       <c r="E2205" s="1" t="s">
-        <v>6882</v>
+        <v>6873</v>
       </c>
     </row>
     <row r="2206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2206" s="1" t="s">
-        <v>6883</v>
+        <v>6874</v>
       </c>
       <c r="B2206" s="1" t="s">
-        <v>25</v>
+        <v>1399</v>
       </c>
       <c r="C2206" s="1" t="s">
-        <v>6884</v>
+        <v>6875</v>
       </c>
       <c r="E2206" s="1" t="s">
-        <v>6885</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="2207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2207" s="1" t="s">
-        <v>6886</v>
+        <v>6877</v>
       </c>
       <c r="B2207" s="1" t="s">
-        <v>25</v>
+        <v>1399</v>
       </c>
       <c r="C2207" s="1" t="s">
-        <v>6887</v>
+        <v>6878</v>
       </c>
       <c r="E2207" s="1" t="s">
-        <v>6638</v>
+        <v>6879</v>
       </c>
     </row>
     <row r="2208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2208" s="1" t="s">
-        <v>6888</v>
+        <v>6880</v>
       </c>
       <c r="B2208" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2208" s="1" t="s">
-        <v>6889</v>
+        <v>6881</v>
       </c>
       <c r="E2208" s="1" t="s">
-        <v>6890</v>
+        <v>6882</v>
       </c>
     </row>
     <row r="2209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2209" s="1" t="s">
-        <v>6891</v>
+        <v>6883</v>
       </c>
       <c r="B2209" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2209" s="1" t="s">
-        <v>6892</v>
+        <v>6884</v>
       </c>
       <c r="E2209" s="1" t="s">
-        <v>6893</v>
+        <v>6885</v>
       </c>
     </row>
     <row r="2210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2210" s="1" t="s">
-        <v>6894</v>
+        <v>6886</v>
       </c>
       <c r="B2210" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2210" s="1" t="s">
-        <v>6895</v>
-      </c>
-      <c r="D2210" s="1" t="s">
-        <v>445</v>
+        <v>6887</v>
       </c>
       <c r="E2210" s="1" t="s">
-        <v>6896</v>
+        <v>6638</v>
       </c>
     </row>
     <row r="2211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2211" s="1" t="s">
-        <v>6897</v>
+        <v>6888</v>
       </c>
       <c r="B2211" s="1" t="s">
-        <v>374</v>
+        <v>25</v>
       </c>
       <c r="C2211" s="1" t="s">
-        <v>6898</v>
-      </c>
-      <c r="D2211" s="1" t="s">
-        <v>445</v>
+        <v>6889</v>
       </c>
       <c r="E2211" s="1" t="s">
-        <v>6899</v>
+        <v>6890</v>
       </c>
     </row>
     <row r="2212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2212" s="1" t="s">
-        <v>6900</v>
+        <v>6891</v>
       </c>
       <c r="B2212" s="1" t="s">
-        <v>374</v>
+        <v>25</v>
       </c>
       <c r="C2212" s="1" t="s">
-        <v>6901</v>
-      </c>
-      <c r="D2212" s="1" t="s">
-        <v>6902</v>
+        <v>6892</v>
       </c>
       <c r="E2212" s="1" t="s">
-        <v>6903</v>
+        <v>6893</v>
       </c>
     </row>
     <row r="2213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2213" s="1" t="s">
-        <v>6939</v>
+        <v>6894</v>
       </c>
       <c r="B2213" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C2213" s="1" t="s">
-        <v>6940</v>
+        <v>6895</v>
       </c>
       <c r="D2213" s="1" t="s">
-        <v>6941</v>
+        <v>445</v>
       </c>
       <c r="E2213" s="1" t="s">
-        <v>6942</v>
+        <v>6896</v>
       </c>
     </row>
     <row r="2214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2214" s="1" t="s">
-        <v>6904</v>
+        <v>6897</v>
       </c>
       <c r="B2214" s="1" t="s">
-        <v>186</v>
+        <v>374</v>
       </c>
       <c r="C2214" s="1" t="s">
-        <v>6905</v>
+        <v>6898</v>
       </c>
       <c r="D2214" s="1" t="s">
-        <v>6583</v>
+        <v>445</v>
       </c>
       <c r="E2214" s="1" t="s">
-        <v>6906</v>
+        <v>6899</v>
       </c>
     </row>
     <row r="2215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2215" s="1" t="s">
-        <v>6907</v>
+        <v>6900</v>
       </c>
       <c r="B2215" s="1" t="s">
-        <v>186</v>
+        <v>374</v>
       </c>
       <c r="C2215" s="1" t="s">
-        <v>6908</v>
+        <v>6901</v>
       </c>
       <c r="D2215" s="1" t="s">
-        <v>6584</v>
+        <v>6902</v>
       </c>
       <c r="E2215" s="1" t="s">
-        <v>6909</v>
+        <v>6903</v>
       </c>
     </row>
     <row r="2216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2216" s="1" t="s">
-        <v>6910</v>
+        <v>6939</v>
       </c>
       <c r="B2216" s="1" t="s">
-        <v>1399</v>
+        <v>25</v>
       </c>
       <c r="C2216" s="1" t="s">
-        <v>6911</v>
+        <v>6940</v>
       </c>
       <c r="D2216" s="1" t="s">
-        <v>445</v>
+        <v>6941</v>
       </c>
       <c r="E2216" s="1" t="s">
-        <v>6912</v>
+        <v>6942</v>
       </c>
     </row>
     <row r="2217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2217" s="1" t="s">
-        <v>6913</v>
+        <v>6904</v>
       </c>
       <c r="B2217" s="1" t="s">
-        <v>1399</v>
+        <v>186</v>
       </c>
       <c r="C2217" s="1" t="s">
-        <v>6914</v>
+        <v>6905</v>
+      </c>
+      <c r="D2217" s="1" t="s">
+        <v>6583</v>
       </c>
       <c r="E2217" s="1" t="s">
-        <v>6915</v>
+        <v>6906</v>
       </c>
     </row>
     <row r="2218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2218" s="1" t="s">
-        <v>6916</v>
+        <v>6907</v>
       </c>
       <c r="B2218" s="1" t="s">
-        <v>6593</v>
+        <v>186</v>
       </c>
       <c r="C2218" s="1" t="s">
-        <v>6917</v>
+        <v>6908</v>
       </c>
       <c r="D2218" s="1" t="s">
-        <v>6918</v>
+        <v>6584</v>
       </c>
       <c r="E2218" s="1" t="s">
-        <v>6919</v>
+        <v>6909</v>
       </c>
     </row>
     <row r="2219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2219" s="1" t="s">
-        <v>6920</v>
+        <v>6910</v>
       </c>
       <c r="B2219" s="1" t="s">
-        <v>6593</v>
+        <v>1399</v>
       </c>
       <c r="C2219" s="1" t="s">
-        <v>6921</v>
+        <v>6911</v>
+      </c>
+      <c r="D2219" s="1" t="s">
+        <v>445</v>
       </c>
       <c r="E2219" s="1" t="s">
-        <v>6922</v>
+        <v>6912</v>
       </c>
     </row>
     <row r="2220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2220" s="1" t="s">
-        <v>6923</v>
+        <v>6913</v>
       </c>
       <c r="B2220" s="1" t="s">
-        <v>6593</v>
+        <v>1399</v>
       </c>
       <c r="C2220" s="1" t="s">
-        <v>6924</v>
-      </c>
-      <c r="D2220" s="1" t="s">
-        <v>6594</v>
+        <v>6914</v>
       </c>
       <c r="E2220" s="1" t="s">
-        <v>6925</v>
+        <v>6915</v>
       </c>
     </row>
     <row r="2221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2221" s="1" t="s">
-        <v>6926</v>
+        <v>6916</v>
       </c>
       <c r="B2221" s="1" t="s">
         <v>6593</v>
       </c>
       <c r="C2221" s="1" t="s">
-        <v>6927</v>
+        <v>6917</v>
+      </c>
+      <c r="D2221" s="1" t="s">
+        <v>6918</v>
       </c>
       <c r="E2221" s="1" t="s">
-        <v>464</v>
+        <v>6919</v>
       </c>
     </row>
     <row r="2222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2222" s="1" t="s">
-        <v>6928</v>
+        <v>6920</v>
       </c>
       <c r="B2222" s="1" t="s">
         <v>6593</v>
       </c>
       <c r="C2222" s="1" t="s">
-        <v>6929</v>
-      </c>
-      <c r="D2222" s="1" t="s">
-        <v>445</v>
+        <v>6921</v>
       </c>
       <c r="E2222" s="1" t="s">
-        <v>6930</v>
+        <v>6922</v>
       </c>
     </row>
     <row r="2223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2223" s="1" t="s">
-        <v>6931</v>
+        <v>6923</v>
       </c>
       <c r="B2223" s="1" t="s">
         <v>6593</v>
       </c>
       <c r="C2223" s="1" t="s">
-        <v>6932</v>
+        <v>6924</v>
+      </c>
+      <c r="D2223" s="1" t="s">
+        <v>6594</v>
       </c>
       <c r="E2223" s="1" t="s">
-        <v>6933</v>
+        <v>6925</v>
       </c>
     </row>
     <row r="2224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2224" s="1" t="s">
-        <v>6934</v>
+        <v>6926</v>
       </c>
       <c r="B2224" s="1" t="s">
         <v>6593</v>
       </c>
       <c r="C2224" s="1" t="s">
-        <v>6935</v>
-      </c>
-      <c r="D2224" s="1" t="s">
-        <v>6595</v>
+        <v>6927</v>
       </c>
       <c r="E2224" s="1" t="s">
-        <v>6936</v>
+        <v>464</v>
       </c>
     </row>
     <row r="2225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2225" s="1" t="s">
-        <v>6937</v>
+        <v>6928</v>
       </c>
       <c r="B2225" s="1" t="s">
         <v>6593</v>
       </c>
       <c r="C2225" s="1" t="s">
-        <v>6938</v>
+        <v>6929</v>
       </c>
       <c r="D2225" s="1" t="s">
         <v>445</v>
       </c>
       <c r="E2225" s="1" t="s">
-        <v>3891</v>
+        <v>6930</v>
       </c>
     </row>
     <row r="2226" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2226" s="1" t="s">
-        <v>6596</v>
+        <v>6931</v>
       </c>
       <c r="B2226" s="1" t="s">
         <v>6593</v>
       </c>
       <c r="C2226" s="1" t="s">
-        <v>6597</v>
+        <v>6932</v>
       </c>
       <c r="E2226" s="1" t="s">
-        <v>6598</v>
+        <v>6933</v>
       </c>
     </row>
     <row r="2227" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2227" s="1" t="s">
-        <v>6599</v>
+        <v>6934</v>
       </c>
       <c r="B2227" s="1" t="s">
         <v>6593</v>
       </c>
       <c r="C2227" s="1" t="s">
+        <v>6935</v>
+      </c>
+      <c r="D2227" s="1" t="s">
+        <v>6595</v>
+      </c>
+      <c r="E2227" s="1" t="s">
+        <v>6936</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2228" s="1" t="s">
+        <v>6937</v>
+      </c>
+      <c r="B2228" s="1" t="s">
+        <v>6593</v>
+      </c>
+      <c r="C2228" s="1" t="s">
+        <v>6938</v>
+      </c>
+      <c r="D2228" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E2228" s="1" t="s">
+        <v>3891</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2229" s="1" t="s">
+        <v>6596</v>
+      </c>
+      <c r="B2229" s="1" t="s">
+        <v>6593</v>
+      </c>
+      <c r="C2229" s="1" t="s">
+        <v>6597</v>
+      </c>
+      <c r="E2229" s="1" t="s">
+        <v>6598</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2230" s="1" t="s">
+        <v>6599</v>
+      </c>
+      <c r="B2230" s="1" t="s">
+        <v>6593</v>
+      </c>
+      <c r="C2230" s="1" t="s">
         <v>6600</v>
       </c>
-      <c r="D2227" s="1" t="s">
+      <c r="D2230" s="1" t="s">
         <v>6601</v>
       </c>
-      <c r="E2227" s="1" t="s">
+      <c r="E2230" s="1" t="s">
         <v>6602</v>
       </c>
     </row>
